--- a/04-Development-and-Quality-Assurance/Evaluation-Testing/Logs/Kali/Kali_Data.xlsx
+++ b/04-Development-and-Quality-Assurance/Evaluation-Testing/Logs/Kali/Kali_Data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://autuni-my.sharepoint.com/personal/cgr2690_autuni_ac_nz/Documents/Data/COMP703/Linux Networking/04-Development-and-Quality-Assurance/Logs/Kali/Run8/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://autuni-my.sharepoint.com/personal/cgr2690_autuni_ac_nz/Documents/Data/COMP703/Linux Networking/04-Development-and-Quality-Assurance/Evaluation-Testing/Logs/Kali/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="154" documentId="11_1A0B8F4F527255435991DA6AD05ADE5EEEC8095E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{73CFE85B-5EE4-43CD-83F9-EF9FF7600F06}"/>
+  <xr:revisionPtr revIDLastSave="173" documentId="11_1A0B8F4F527255435991DA6AD05ADE5EEEC8095E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A41112F3-AD76-4E73-8CB7-4BD845B0DE46}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="526" uniqueCount="39">
   <si>
     <t>128</t>
   </si>
@@ -149,12 +149,18 @@
   <si>
     <t>IPv6 UDP</t>
   </si>
+  <si>
+    <t>IPv4</t>
+  </si>
+  <si>
+    <t>IPv6</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -162,13 +168,32 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="24"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -183,11 +208,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -285,7 +314,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$C$3</c:f>
+              <c:f>Sheet1!$C$6</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -320,7 +349,7 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$B$4:$B$15</c:f>
+              <c:f>Sheet1!$B$7:$B$18</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="12"/>
@@ -365,7 +394,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$C$4:$C$15</c:f>
+              <c:f>Sheet1!$C$7:$C$18</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="12"/>
@@ -420,7 +449,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$I$3</c:f>
+              <c:f>Sheet1!$I$6</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -455,7 +484,7 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$B$4:$B$15</c:f>
+              <c:f>Sheet1!$B$7:$B$18</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="12"/>
@@ -500,7 +529,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$I$4:$I$15</c:f>
+              <c:f>Sheet1!$I$7:$I$18</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="12"/>
@@ -831,7 +860,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$D$3</c:f>
+              <c:f>Sheet1!$D$6</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -866,7 +895,7 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$B$4:$B$15</c:f>
+              <c:f>Sheet1!$B$7:$B$18</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="12"/>
@@ -911,7 +940,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$D$4:$D$15</c:f>
+              <c:f>Sheet1!$D$7:$D$18</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="12"/>
@@ -966,7 +995,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$J$3</c:f>
+              <c:f>Sheet1!$J$6</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1001,7 +1030,7 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$B$4:$B$15</c:f>
+              <c:f>Sheet1!$B$7:$B$18</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="12"/>
@@ -1046,7 +1075,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$J$4:$J$15</c:f>
+              <c:f>Sheet1!$J$7:$J$18</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="12"/>
@@ -1327,7 +1356,7 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-NZ"/>
-              <a:t>Average BitRate</a:t>
+              <a:t>Average Bitrate</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -1372,7 +1401,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$E$3</c:f>
+              <c:f>Sheet1!$E$6</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1407,7 +1436,7 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$B$4:$B$15</c:f>
+              <c:f>Sheet1!$B$7:$B$18</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="12"/>
@@ -1452,7 +1481,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$E$4:$E$15</c:f>
+              <c:f>Sheet1!$E$7:$E$18</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="12"/>
@@ -1507,7 +1536,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$K$3</c:f>
+              <c:f>Sheet1!$K$6</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1542,7 +1571,7 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$B$4:$B$15</c:f>
+              <c:f>Sheet1!$B$7:$B$18</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="12"/>
@@ -1587,7 +1616,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$K$4:$K$15</c:f>
+              <c:f>Sheet1!$K$7:$K$18</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="12"/>
@@ -1868,7 +1897,7 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-NZ"/>
-              <a:t>Average Packet Loss</a:t>
+              <a:t>Average Packetloss</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -1913,7 +1942,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$F$3</c:f>
+              <c:f>Sheet1!$F$6</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1948,7 +1977,7 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$B$4:$B$15</c:f>
+              <c:f>Sheet1!$B$7:$B$18</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="12"/>
@@ -1993,7 +2022,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$F$4:$F$15</c:f>
+              <c:f>Sheet1!$F$7:$F$18</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="12"/>
@@ -2048,7 +2077,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$L$3</c:f>
+              <c:f>Sheet1!$L$6</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2083,7 +2112,7 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$B$4:$B$15</c:f>
+              <c:f>Sheet1!$B$7:$B$18</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="12"/>
@@ -2128,7 +2157,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$L$4:$L$15</c:f>
+              <c:f>Sheet1!$L$7:$L$18</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="12"/>
@@ -2461,7 +2490,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$T$3</c:f>
+              <c:f>Sheet1!$T$6</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2496,7 +2525,7 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$S$4:$S$15</c:f>
+              <c:f>Sheet1!$S$7:$S$18</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="12"/>
@@ -2541,7 +2570,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$T$4:$T$15</c:f>
+              <c:f>Sheet1!$T$7:$T$18</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="12"/>
@@ -2596,7 +2625,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$Z$3</c:f>
+              <c:f>Sheet1!$Z$6</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2631,7 +2660,7 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$S$4:$S$15</c:f>
+              <c:f>Sheet1!$S$7:$S$18</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="12"/>
@@ -2676,7 +2705,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$Z$4:$Z$15</c:f>
+              <c:f>Sheet1!$Z$7:$Z$18</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="12"/>
@@ -3009,7 +3038,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$U$3</c:f>
+              <c:f>Sheet1!$U$6</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3044,7 +3073,7 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$S$4:$S$15</c:f>
+              <c:f>Sheet1!$S$7:$S$18</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="12"/>
@@ -3089,7 +3118,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$U$4:$U$15</c:f>
+              <c:f>Sheet1!$U$7:$U$18</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="12"/>
@@ -3144,7 +3173,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$AA$3</c:f>
+              <c:f>Sheet1!$AA$6</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3179,7 +3208,7 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$S$4:$S$15</c:f>
+              <c:f>Sheet1!$S$7:$S$18</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="12"/>
@@ -3224,7 +3253,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$AA$4:$AA$15</c:f>
+              <c:f>Sheet1!$AA$7:$AA$18</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="12"/>
@@ -3512,7 +3541,7 @@
                   </a:sysClr>
                 </a:solidFill>
               </a:rPr>
-              <a:t>Average BitRate</a:t>
+              <a:t>Average Bitrate</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -3557,7 +3586,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$V$3</c:f>
+              <c:f>Sheet1!$V$6</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3592,7 +3621,7 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$S$4:$S$15</c:f>
+              <c:f>Sheet1!$S$7:$S$18</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="12"/>
@@ -3637,7 +3666,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$V$4:$V$15</c:f>
+              <c:f>Sheet1!$V$7:$V$18</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="12"/>
@@ -3692,7 +3721,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$AB$3</c:f>
+              <c:f>Sheet1!$AB$6</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3727,7 +3756,7 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$S$4:$S$15</c:f>
+              <c:f>Sheet1!$S$7:$S$18</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="12"/>
@@ -3772,7 +3801,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$AB$4:$AB$15</c:f>
+              <c:f>Sheet1!$AB$7:$AB$18</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="12"/>
@@ -4060,7 +4089,7 @@
                   </a:sysClr>
                 </a:solidFill>
               </a:rPr>
-              <a:t>Average Packet Loss</a:t>
+              <a:t>Average Packetloss</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -4105,7 +4134,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$W$3</c:f>
+              <c:f>Sheet1!$W$6</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -4140,7 +4169,7 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$S$4:$S$15</c:f>
+              <c:f>Sheet1!$S$7:$S$18</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="12"/>
@@ -4185,7 +4214,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$W$4:$W$15</c:f>
+              <c:f>Sheet1!$W$7:$W$18</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="12"/>
@@ -4240,7 +4269,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$AC$3</c:f>
+              <c:f>Sheet1!$AC$6</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -4275,7 +4304,7 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$S$4:$S$15</c:f>
+              <c:f>Sheet1!$S$7:$S$18</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="12"/>
@@ -4320,7 +4349,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$AC$4:$AC$15</c:f>
+              <c:f>Sheet1!$AC$7:$AC$18</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="12"/>
@@ -8915,15 +8944,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>588307</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>169209</xdr:rowOff>
+      <xdr:colOff>442630</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>12327</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>319366</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>54909</xdr:rowOff>
+      <xdr:colOff>173689</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>88527</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -8951,15 +8980,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>539483</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>155601</xdr:rowOff>
+      <xdr:colOff>393806</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>189219</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>270543</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>41301</xdr:rowOff>
+      <xdr:colOff>124866</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>74919</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -8987,15 +9016,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>397808</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>179613</xdr:rowOff>
+      <xdr:colOff>252131</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>22731</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>128866</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>65313</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>588306</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>98931</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -9023,15 +9052,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>360189</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>168407</xdr:rowOff>
+      <xdr:colOff>214512</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>11525</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>91248</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>54107</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>550688</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>87725</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -9058,16 +9087,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>588308</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>169209</xdr:rowOff>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>16807</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>23532</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>25</xdr:col>
-      <xdr:colOff>319367</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>54909</xdr:rowOff>
+      <xdr:colOff>352984</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>99732</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -9094,16 +9123,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>587508</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>103576</xdr:rowOff>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>16007</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>148399</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>25</xdr:col>
-      <xdr:colOff>318566</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>179776</xdr:rowOff>
+      <xdr:colOff>352183</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>34099</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -9131,15 +9160,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>25</xdr:col>
-      <xdr:colOff>377796</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>4322</xdr:rowOff>
+      <xdr:colOff>411413</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>49145</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>33</xdr:col>
-      <xdr:colOff>108855</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>80522</xdr:rowOff>
+      <xdr:colOff>142472</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>125345</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -9167,15 +9196,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>25</xdr:col>
-      <xdr:colOff>397008</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>108377</xdr:rowOff>
+      <xdr:colOff>430625</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>153200</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>33</xdr:col>
-      <xdr:colOff>128067</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>184577</xdr:rowOff>
+      <xdr:colOff>161684</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>38900</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -9201,10 +9230,6 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -9492,851 +9517,920 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{241AF353-C3A0-40A6-A389-2EE7141C0FF3}">
-  <dimension ref="B2:AC15"/>
+  <dimension ref="B2:AG18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="17" max="18" width="9.140625" style="3"/>
+  </cols>
   <sheetData>
-    <row r="2" spans="2:29" x14ac:dyDescent="0.25">
-      <c r="B2" s="1" t="s">
+    <row r="2" spans="2:33" x14ac:dyDescent="0.25">
+      <c r="B2" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
+      <c r="N2" s="2"/>
+      <c r="O2" s="2"/>
+      <c r="T2" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="U2" s="2"/>
+      <c r="V2" s="2"/>
+      <c r="W2" s="2"/>
+      <c r="X2" s="2"/>
+      <c r="Y2" s="2"/>
+      <c r="Z2" s="2"/>
+      <c r="AA2" s="2"/>
+      <c r="AB2" s="2"/>
+      <c r="AC2" s="2"/>
+      <c r="AD2" s="2"/>
+      <c r="AE2" s="2"/>
+      <c r="AF2" s="2"/>
+      <c r="AG2" s="2"/>
+    </row>
+    <row r="3" spans="2:33" x14ac:dyDescent="0.25">
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
+      <c r="N3" s="2"/>
+      <c r="O3" s="2"/>
+      <c r="T3" s="2"/>
+      <c r="U3" s="2"/>
+      <c r="V3" s="2"/>
+      <c r="W3" s="2"/>
+      <c r="X3" s="2"/>
+      <c r="Y3" s="2"/>
+      <c r="Z3" s="2"/>
+      <c r="AA3" s="2"/>
+      <c r="AB3" s="2"/>
+      <c r="AC3" s="2"/>
+      <c r="AD3" s="2"/>
+      <c r="AE3" s="2"/>
+      <c r="AF3" s="2"/>
+      <c r="AG3" s="2"/>
+    </row>
+    <row r="5" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="H2" s="1" t="s">
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="H5" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="S2" s="1" t="s">
+      <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1"/>
+      <c r="L5" s="1"/>
+      <c r="S5" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="T2" s="1"/>
-      <c r="U2" s="1"/>
-      <c r="V2" s="1"/>
-      <c r="W2" s="1"/>
-      <c r="Y2" s="1" t="s">
+      <c r="T5" s="1"/>
+      <c r="U5" s="1"/>
+      <c r="V5" s="1"/>
+      <c r="W5" s="1"/>
+      <c r="Y5" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="Z2" s="1"/>
-      <c r="AA2" s="1"/>
-      <c r="AB2" s="1"/>
-      <c r="AC2" s="1"/>
-    </row>
-    <row r="3" spans="2:29" x14ac:dyDescent="0.25">
-      <c r="B3" t="s">
+      <c r="Z5" s="1"/>
+      <c r="AA5" s="1"/>
+      <c r="AB5" s="1"/>
+      <c r="AC5" s="1"/>
+    </row>
+    <row r="6" spans="2:33" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
         <v>10</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C6" t="s">
         <v>25</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D6" t="s">
         <v>26</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E6" t="s">
         <v>27</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F6" t="s">
         <v>28</v>
       </c>
-      <c r="H3" t="s">
+      <c r="H6" t="s">
         <v>10</v>
       </c>
-      <c r="I3" t="s">
+      <c r="I6" t="s">
         <v>29</v>
       </c>
-      <c r="J3" t="s">
+      <c r="J6" t="s">
         <v>30</v>
       </c>
-      <c r="K3" t="s">
+      <c r="K6" t="s">
         <v>31</v>
       </c>
-      <c r="L3" t="s">
+      <c r="L6" t="s">
         <v>32</v>
       </c>
-      <c r="S3" t="s">
+      <c r="S6" t="s">
         <v>10</v>
       </c>
-      <c r="T3" t="s">
+      <c r="T6" t="s">
         <v>25</v>
       </c>
-      <c r="U3" t="s">
+      <c r="U6" t="s">
         <v>26</v>
       </c>
-      <c r="V3" t="s">
+      <c r="V6" t="s">
         <v>27</v>
       </c>
-      <c r="W3" t="s">
+      <c r="W6" t="s">
         <v>28</v>
       </c>
-      <c r="Y3" t="s">
+      <c r="Y6" t="s">
         <v>10</v>
       </c>
-      <c r="Z3" t="s">
+      <c r="Z6" t="s">
         <v>29</v>
       </c>
-      <c r="AA3" t="s">
+      <c r="AA6" t="s">
         <v>30</v>
       </c>
-      <c r="AB3" t="s">
+      <c r="AB6" t="s">
         <v>31</v>
       </c>
-      <c r="AC3" t="s">
+      <c r="AC6" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="2:29" x14ac:dyDescent="0.25">
-      <c r="B4">
+    <row r="7" spans="2:33" x14ac:dyDescent="0.25">
+      <c r="B7">
         <v>128</v>
       </c>
-      <c r="C4">
+      <c r="C7">
         <v>5.1900000000000004E-4</v>
       </c>
-      <c r="D4">
+      <c r="D7">
         <v>9.8499999999999995E-5</v>
       </c>
-      <c r="E4">
+      <c r="E7">
         <v>17245.820185099998</v>
       </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
-      <c r="H4">
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="H7">
         <v>128</v>
       </c>
-      <c r="I4">
+      <c r="I7">
         <v>3.9450000000000005E-4</v>
       </c>
-      <c r="J4">
+      <c r="J7">
         <v>4.6299999999999994E-5</v>
       </c>
-      <c r="K4">
+      <c r="K7">
         <v>17456.933687000001</v>
       </c>
-      <c r="L4">
+      <c r="L7">
         <v>0.09</v>
       </c>
-      <c r="S4">
+      <c r="S7">
         <v>128</v>
       </c>
-      <c r="T4">
+      <c r="T7">
         <v>5.9690000000000003E-4</v>
       </c>
-      <c r="U4">
+      <c r="U7">
         <v>9.7E-5</v>
       </c>
-      <c r="V4">
+      <c r="V7">
         <v>17261.783222099999</v>
       </c>
-      <c r="W4">
-        <v>0</v>
-      </c>
-      <c r="Y4">
+      <c r="W7">
+        <v>0</v>
+      </c>
+      <c r="Y7">
         <v>128</v>
       </c>
-      <c r="Z4">
+      <c r="Z7">
         <v>1.305E-4</v>
       </c>
-      <c r="AA4">
+      <c r="AA7">
         <v>4.6099999999999996E-5</v>
       </c>
-      <c r="AB4">
+      <c r="AB7">
         <v>17449.604368099997</v>
       </c>
-      <c r="AC4">
+      <c r="AC7">
         <v>5.2000000000000005E-2</v>
       </c>
     </row>
-    <row r="5" spans="2:29" x14ac:dyDescent="0.25">
-      <c r="B5">
+    <row r="8" spans="2:33" x14ac:dyDescent="0.25">
+      <c r="B8">
         <v>256</v>
       </c>
-      <c r="C5">
+      <c r="C8">
         <v>5.1509999999999989E-4</v>
       </c>
-      <c r="D5">
+      <c r="D8">
         <v>9.0400000000000015E-5</v>
       </c>
-      <c r="E5">
+      <c r="E8">
         <v>34804.3220115</v>
       </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
-      <c r="H5">
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="H8">
         <v>256</v>
       </c>
-      <c r="I5">
+      <c r="I8">
         <v>4.3400000000000003E-4</v>
       </c>
-      <c r="J5">
+      <c r="J8">
         <v>4.7099999999999993E-5</v>
       </c>
-      <c r="K5">
+      <c r="K8">
         <v>34942.620202500002</v>
       </c>
-      <c r="L5">
+      <c r="L8">
         <v>6.0000000000000012E-2</v>
       </c>
-      <c r="S5">
+      <c r="S8">
         <v>256</v>
       </c>
-      <c r="T5">
+      <c r="T8">
         <v>5.5079999999999994E-4</v>
       </c>
-      <c r="U5">
+      <c r="U8">
         <v>9.0300000000000013E-5</v>
       </c>
-      <c r="V5">
+      <c r="V8">
         <v>34817.985176900009</v>
       </c>
-      <c r="W5">
-        <v>0</v>
-      </c>
-      <c r="Y5">
+      <c r="W8">
+        <v>0</v>
+      </c>
+      <c r="Y8">
         <v>256</v>
       </c>
-      <c r="Z5">
+      <c r="Z8">
         <v>1.651E-4</v>
       </c>
-      <c r="AA5">
+      <c r="AA8">
         <v>4.7000000000000004E-5</v>
       </c>
-      <c r="AB5">
+      <c r="AB8">
         <v>34920.658910500002</v>
       </c>
-      <c r="AC5">
+      <c r="AC8">
         <v>6.4000000000000015E-2</v>
       </c>
     </row>
-    <row r="6" spans="2:29" x14ac:dyDescent="0.25">
-      <c r="B6">
+    <row r="9" spans="2:33" x14ac:dyDescent="0.25">
+      <c r="B9">
         <v>384</v>
       </c>
-      <c r="C6">
+      <c r="C9">
         <v>8.8909999999999998E-4</v>
       </c>
-      <c r="D6">
+      <c r="D9">
         <v>8.7799999999999993E-5</v>
       </c>
-      <c r="E6">
+      <c r="E9">
         <v>52601.005454100006</v>
       </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="H6">
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="H9">
         <v>384</v>
       </c>
-      <c r="I6">
+      <c r="I9">
         <v>4.3939999999999995E-4</v>
       </c>
-      <c r="J6">
+      <c r="J9">
         <v>4.4600000000000007E-5</v>
       </c>
-      <c r="K6">
+      <c r="K9">
         <v>52154.577835999997</v>
       </c>
-      <c r="L6">
+      <c r="L9">
         <v>6.0000000000000012E-2</v>
       </c>
-      <c r="S6">
+      <c r="S9">
         <v>384</v>
       </c>
-      <c r="T6">
+      <c r="T9">
         <v>9.2360000000000012E-4</v>
       </c>
-      <c r="U6">
+      <c r="U9">
         <v>8.8299999999999978E-5</v>
       </c>
-      <c r="V6">
+      <c r="V9">
         <v>52553.033332400002</v>
       </c>
-      <c r="W6">
-        <v>0</v>
-      </c>
-      <c r="Y6">
+      <c r="W9">
+        <v>0</v>
+      </c>
+      <c r="Y9">
         <v>384</v>
       </c>
-      <c r="Z6">
+      <c r="Z9">
         <v>1.9290000000000003E-4</v>
       </c>
-      <c r="AA6">
+      <c r="AA9">
         <v>4.4299999999999993E-5</v>
       </c>
-      <c r="AB6">
+      <c r="AB9">
         <v>52295.464183899996</v>
       </c>
-      <c r="AC6">
+      <c r="AC9">
         <v>5.6000000000000008E-2</v>
       </c>
     </row>
-    <row r="7" spans="2:29" x14ac:dyDescent="0.25">
-      <c r="B7">
+    <row r="10" spans="2:33" x14ac:dyDescent="0.25">
+      <c r="B10">
         <v>512</v>
       </c>
-      <c r="C7">
+      <c r="C10">
         <v>9.3680000000000011E-4</v>
       </c>
-      <c r="D7">
+      <c r="D10">
         <v>8.5400000000000016E-5</v>
       </c>
-      <c r="E7">
+      <c r="E10">
         <v>70083.514447100009</v>
       </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
-      <c r="H7">
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="H10">
         <v>512</v>
       </c>
-      <c r="I7">
+      <c r="I10">
         <v>4.1780000000000002E-4</v>
       </c>
-      <c r="J7">
+      <c r="J10">
         <v>3.4700000000000003E-5</v>
       </c>
-      <c r="K7">
+      <c r="K10">
         <v>69797.020971200007</v>
       </c>
-      <c r="L7">
+      <c r="L10">
         <v>0.10800000000000001</v>
       </c>
-      <c r="S7">
+      <c r="S10">
         <v>512</v>
       </c>
-      <c r="T7">
+      <c r="T10">
         <v>6.4900000000000005E-4</v>
       </c>
-      <c r="U7">
+      <c r="U10">
         <v>8.3399999999999994E-5</v>
       </c>
-      <c r="V7">
+      <c r="V10">
         <v>70126.190825999991</v>
       </c>
-      <c r="W7">
-        <v>0</v>
-      </c>
-      <c r="Y7">
+      <c r="W10">
+        <v>0</v>
+      </c>
+      <c r="Y10">
         <v>512</v>
       </c>
-      <c r="Z7">
+      <c r="Z10">
         <v>1.9689999999999999E-4</v>
       </c>
-      <c r="AA7">
+      <c r="AA10">
         <v>3.4099999999999995E-5</v>
       </c>
-      <c r="AB7">
+      <c r="AB10">
         <v>69766.4187676</v>
       </c>
-      <c r="AC7">
+      <c r="AC10">
         <v>5.3000000000000005E-2</v>
       </c>
     </row>
-    <row r="8" spans="2:29" x14ac:dyDescent="0.25">
-      <c r="B8">
+    <row r="11" spans="2:33" x14ac:dyDescent="0.25">
+      <c r="B11">
         <v>640</v>
       </c>
-      <c r="C8">
+      <c r="C11">
         <v>1.0509E-3</v>
       </c>
-      <c r="D8">
+      <c r="D11">
         <v>8.6300000000000011E-5</v>
       </c>
-      <c r="E8">
+      <c r="E11">
         <v>87896.877479699993</v>
       </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
-      <c r="H8">
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="H11">
         <v>640</v>
       </c>
-      <c r="I8">
+      <c r="I11">
         <v>4.103E-4</v>
       </c>
-      <c r="J8">
+      <c r="J11">
         <v>2.5100000000000004E-5</v>
       </c>
-      <c r="K8">
+      <c r="K11">
         <v>86995.931843299986</v>
       </c>
-      <c r="L8">
+      <c r="L11">
         <v>5.2000000000000005E-2</v>
       </c>
-      <c r="S8">
+      <c r="S11">
         <v>640</v>
       </c>
-      <c r="T8">
+      <c r="T11">
         <v>8.3900000000000001E-4</v>
       </c>
-      <c r="U8">
+      <c r="U11">
         <v>8.5900000000000014E-5</v>
       </c>
-      <c r="V8">
+      <c r="V11">
         <v>88080.382773500009</v>
       </c>
-      <c r="W8">
-        <v>0</v>
-      </c>
-      <c r="Y8">
+      <c r="W11">
+        <v>0</v>
+      </c>
+      <c r="Y11">
         <v>640</v>
       </c>
-      <c r="Z8">
+      <c r="Z11">
         <v>2.1990000000000001E-4</v>
       </c>
-      <c r="AA8">
+      <c r="AA11">
         <v>2.5600000000000006E-5</v>
       </c>
-      <c r="AB8">
+      <c r="AB11">
         <v>87305.134951700005</v>
       </c>
-      <c r="AC8">
+      <c r="AC11">
         <v>0.11899999999999999</v>
       </c>
     </row>
-    <row r="9" spans="2:29" x14ac:dyDescent="0.25">
-      <c r="B9">
+    <row r="12" spans="2:33" x14ac:dyDescent="0.25">
+      <c r="B12">
         <v>768</v>
       </c>
-      <c r="C9">
+      <c r="C12">
         <v>7.17309E-2</v>
       </c>
-      <c r="D9">
+      <c r="D12">
         <v>1.2000000000000002E-4</v>
       </c>
-      <c r="E9">
+      <c r="E12">
         <v>93581.590693999999</v>
       </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
-      <c r="H9">
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="H12">
         <v>768</v>
       </c>
-      <c r="I9">
+      <c r="I12">
         <v>5.0905999999999989E-3</v>
       </c>
-      <c r="J9">
+      <c r="J12">
         <v>1.9699999999999999E-4</v>
       </c>
-      <c r="K9">
+      <c r="K12">
         <v>91091.661662600003</v>
       </c>
-      <c r="L9">
+      <c r="L12">
         <v>4.9999999999999996E-2</v>
       </c>
-      <c r="S9">
+      <c r="S12">
         <v>768</v>
       </c>
-      <c r="T9">
+      <c r="T12">
         <v>6.9628200000000001E-2</v>
       </c>
-      <c r="U9">
+      <c r="U12">
         <v>1.2000000000000002E-4</v>
       </c>
-      <c r="V9">
+      <c r="V12">
         <v>93563.075730600001</v>
       </c>
-      <c r="W9">
-        <v>0</v>
-      </c>
-      <c r="Y9">
+      <c r="W12">
+        <v>0</v>
+      </c>
+      <c r="Y12">
         <v>768</v>
       </c>
-      <c r="Z9">
+      <c r="Z12">
         <v>4.9291999999999999E-3</v>
       </c>
-      <c r="AA9">
+      <c r="AA12">
         <v>2.0130000000000001E-4</v>
       </c>
-      <c r="AB9">
+      <c r="AB12">
         <v>91087.538745800004</v>
       </c>
-      <c r="AC9">
+      <c r="AC12">
         <v>6.0000000000000012E-2</v>
       </c>
     </row>
-    <row r="10" spans="2:29" x14ac:dyDescent="0.25">
-      <c r="B10">
+    <row r="13" spans="2:33" x14ac:dyDescent="0.25">
+      <c r="B13">
         <v>896</v>
       </c>
-      <c r="C10">
+      <c r="C13">
         <v>7.6499400000000009E-2</v>
       </c>
-      <c r="D10">
+      <c r="D13">
         <v>1.4100000000000004E-4</v>
       </c>
-      <c r="E10">
+      <c r="E13">
         <v>93572.373676800009</v>
       </c>
-      <c r="F10">
-        <v>0</v>
-      </c>
-      <c r="H10">
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="H13">
         <v>896</v>
       </c>
-      <c r="I10">
+      <c r="I13">
         <v>5.8661999999999994E-3</v>
       </c>
-      <c r="J10">
+      <c r="J13">
         <v>3.9160000000000003E-4</v>
       </c>
-      <c r="K10">
+      <c r="K13">
         <v>92280.248612299998</v>
       </c>
-      <c r="L10">
+      <c r="L13">
         <v>9.9999999999999992E-2</v>
       </c>
-      <c r="S10">
+      <c r="S13">
         <v>896</v>
       </c>
-      <c r="T10">
+      <c r="T13">
         <v>7.6671800000000012E-2</v>
       </c>
-      <c r="U10">
+      <c r="U13">
         <v>1.4090000000000004E-4</v>
       </c>
-      <c r="V10">
+      <c r="V13">
         <v>93584.696719300002</v>
       </c>
-      <c r="W10">
-        <v>0</v>
-      </c>
-      <c r="Y10">
+      <c r="W13">
+        <v>0</v>
+      </c>
+      <c r="Y13">
         <v>896</v>
       </c>
-      <c r="Z10">
+      <c r="Z13">
         <v>5.7063000000000001E-3</v>
       </c>
-      <c r="AA10">
+      <c r="AA13">
         <v>3.9110000000000002E-4</v>
       </c>
-      <c r="AB10">
+      <c r="AB13">
         <v>92320.009301600003</v>
       </c>
-      <c r="AC10">
+      <c r="AC13">
         <v>4.9999999999999996E-2</v>
       </c>
     </row>
-    <row r="11" spans="2:29" x14ac:dyDescent="0.25">
-      <c r="B11">
+    <row r="14" spans="2:33" x14ac:dyDescent="0.25">
+      <c r="B14">
         <v>1024</v>
       </c>
-      <c r="C11">
+      <c r="C14">
         <v>7.5401599999999999E-2</v>
       </c>
-      <c r="D11">
+      <c r="D14">
         <v>1.6150000000000002E-4</v>
       </c>
-      <c r="E11">
+      <c r="E14">
         <v>93631.19045899999</v>
       </c>
-      <c r="F11">
-        <v>0</v>
-      </c>
-      <c r="H11">
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="H14">
         <v>1024</v>
       </c>
-      <c r="I11">
+      <c r="I14">
         <v>6.5946000000000008E-3</v>
       </c>
-      <c r="J11">
+      <c r="J14">
         <v>5.6949999999999991E-4</v>
       </c>
-      <c r="K11">
+      <c r="K14">
         <v>93294.213047600002</v>
       </c>
-      <c r="L11">
+      <c r="L14">
         <v>4.6999999999999993E-2</v>
       </c>
-      <c r="S11">
+      <c r="S14">
         <v>1024</v>
       </c>
-      <c r="T11">
+      <c r="T14">
         <v>7.7855099999999997E-2</v>
       </c>
-      <c r="U11">
+      <c r="U14">
         <v>1.6160000000000002E-4</v>
       </c>
-      <c r="V11">
+      <c r="V14">
         <v>93629.4816096</v>
       </c>
-      <c r="W11">
-        <v>0</v>
-      </c>
-      <c r="Y11">
+      <c r="W14">
+        <v>0</v>
+      </c>
+      <c r="Y14">
         <v>1024</v>
       </c>
-      <c r="Z11">
+      <c r="Z14">
         <v>6.4381000000000004E-3</v>
       </c>
-      <c r="AA11">
+      <c r="AA14">
         <v>5.689E-4</v>
       </c>
-      <c r="AB11">
+      <c r="AB14">
         <v>93239.203584000003</v>
       </c>
-      <c r="AC11">
+      <c r="AC14">
         <v>9.2999999999999985E-2</v>
       </c>
     </row>
-    <row r="12" spans="2:29" x14ac:dyDescent="0.25">
-      <c r="B12">
+    <row r="15" spans="2:33" x14ac:dyDescent="0.25">
+      <c r="B15">
         <v>1152</v>
       </c>
-      <c r="C12">
+      <c r="C15">
         <v>7.8402199999999991E-2</v>
       </c>
-      <c r="D12">
+      <c r="D15">
         <v>1.8190000000000003E-4</v>
       </c>
-      <c r="E12">
+      <c r="E15">
         <v>93644.150759299999</v>
       </c>
-      <c r="F12">
-        <v>0</v>
-      </c>
-      <c r="H12">
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="H15">
         <v>1152</v>
       </c>
-      <c r="I12">
+      <c r="I15">
         <v>7.3479999999999986E-3</v>
       </c>
-      <c r="J12">
+      <c r="J15">
         <v>7.1880000000000002E-4</v>
       </c>
-      <c r="K12">
+      <c r="K15">
         <v>93997.232500200029</v>
       </c>
-      <c r="L12">
+      <c r="L15">
         <v>8.299999999999999E-2</v>
       </c>
-      <c r="S12">
+      <c r="S15">
         <v>1152</v>
       </c>
-      <c r="T12">
+      <c r="T15">
         <v>7.5410699999999983E-2</v>
       </c>
-      <c r="U12">
+      <c r="U15">
         <v>1.8220000000000001E-4</v>
       </c>
-      <c r="V12">
+      <c r="V15">
         <v>93652.038279800006</v>
       </c>
-      <c r="W12">
-        <v>0</v>
-      </c>
-      <c r="Y12">
+      <c r="W15">
+        <v>0</v>
+      </c>
+      <c r="Y15">
         <v>1152</v>
       </c>
-      <c r="Z12">
+      <c r="Z15">
         <v>7.2344999999999996E-3</v>
       </c>
-      <c r="AA12">
+      <c r="AA15">
         <v>7.2959999999999995E-4</v>
       </c>
-      <c r="AB12">
+      <c r="AB15">
         <v>94018.391845100006</v>
       </c>
-      <c r="AC12">
+      <c r="AC15">
         <v>5.2000000000000005E-2</v>
       </c>
     </row>
-    <row r="13" spans="2:29" x14ac:dyDescent="0.25">
-      <c r="B13">
+    <row r="16" spans="2:33" x14ac:dyDescent="0.25">
+      <c r="B16">
         <v>1280</v>
       </c>
-      <c r="C13">
+      <c r="C16">
         <v>7.4444800000000005E-2</v>
       </c>
-      <c r="D13">
+      <c r="D16">
         <v>2.0259999999999999E-4</v>
       </c>
-      <c r="E13">
+      <c r="E16">
         <v>93654.461065800002</v>
       </c>
-      <c r="F13">
-        <v>0</v>
-      </c>
-      <c r="H13">
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="H16">
         <v>1280</v>
       </c>
-      <c r="I13">
+      <c r="I16">
         <v>8.3416000000000011E-3</v>
       </c>
-      <c r="J13">
+      <c r="J16">
         <v>8.5459999999999996E-4</v>
       </c>
-      <c r="K13">
+      <c r="K16">
         <v>94659.673357399995</v>
       </c>
-      <c r="L13">
+      <c r="L16">
         <v>1.8999999999999996E-2</v>
       </c>
-      <c r="S13">
+      <c r="S16">
         <v>1280</v>
       </c>
-      <c r="T13">
+      <c r="T16">
         <v>7.4295299999999995E-2</v>
       </c>
-      <c r="U13">
+      <c r="U16">
         <v>2.0250000000000004E-4</v>
       </c>
-      <c r="V13">
+      <c r="V16">
         <v>93688.74889979999</v>
       </c>
-      <c r="W13">
-        <v>0</v>
-      </c>
-      <c r="Y13">
+      <c r="W16">
+        <v>0</v>
+      </c>
+      <c r="Y16">
         <v>1280</v>
       </c>
-      <c r="Z13">
+      <c r="Z16">
         <v>8.2635E-3</v>
       </c>
-      <c r="AA13">
+      <c r="AA16">
         <v>8.7139999999999993E-4</v>
       </c>
-      <c r="AB13">
+      <c r="AB16">
         <v>94569.700130700017</v>
       </c>
-      <c r="AC13">
+      <c r="AC16">
         <v>3.7999999999999992E-2</v>
       </c>
     </row>
-    <row r="14" spans="2:29" x14ac:dyDescent="0.25">
-      <c r="B14">
+    <row r="17" spans="2:29" x14ac:dyDescent="0.25">
+      <c r="B17">
         <v>1408</v>
       </c>
-      <c r="C14">
+      <c r="C17">
         <v>7.5332099999999999E-2</v>
       </c>
-      <c r="D14">
+      <c r="D17">
         <v>2.2369999999999999E-4</v>
       </c>
-      <c r="E14">
+      <c r="E17">
         <v>93704.911762599993</v>
       </c>
-      <c r="F14">
-        <v>0</v>
-      </c>
-      <c r="H14">
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="H17">
         <v>1408</v>
       </c>
-      <c r="I14">
+      <c r="I17">
         <v>9.0388000000000013E-3</v>
       </c>
-      <c r="J14">
+      <c r="J17">
         <v>9.9430000000000004E-4</v>
       </c>
-      <c r="K14">
+      <c r="K17">
         <v>95043.688907499993</v>
       </c>
-      <c r="L14">
+      <c r="L17">
         <v>0.217</v>
       </c>
-      <c r="S14">
+      <c r="S17">
         <v>1408</v>
       </c>
-      <c r="T14">
+      <c r="T17">
         <v>8.1909099999999999E-2</v>
       </c>
-      <c r="U14">
+      <c r="U17">
         <v>2.2359999999999996E-4</v>
       </c>
-      <c r="V14">
+      <c r="V17">
         <v>93685.618883300005</v>
       </c>
-      <c r="W14">
-        <v>0</v>
-      </c>
-      <c r="Y14">
+      <c r="W17">
+        <v>0</v>
+      </c>
+      <c r="Y17">
         <v>1408</v>
       </c>
-      <c r="Z14">
+      <c r="Z17">
         <v>8.9073999999999993E-3</v>
       </c>
-      <c r="AA14">
+      <c r="AA17">
         <v>9.9170000000000009E-4</v>
       </c>
-      <c r="AB14">
+      <c r="AB17">
         <v>95105.498003800021</v>
       </c>
-      <c r="AC14">
+      <c r="AC17">
         <v>0.14499999999999996</v>
       </c>
     </row>
-    <row r="15" spans="2:29" x14ac:dyDescent="0.25">
-      <c r="B15">
+    <row r="18" spans="2:29" x14ac:dyDescent="0.25">
+      <c r="B18">
         <v>1536</v>
       </c>
-      <c r="C15">
+      <c r="C18">
         <v>6.8223999999999993E-2</v>
       </c>
-      <c r="D15">
+      <c r="D18">
         <v>2.4439999999999998E-4</v>
       </c>
-      <c r="E15">
+      <c r="E18">
         <v>93745.519585699978</v>
       </c>
-      <c r="F15">
-        <v>0</v>
-      </c>
-      <c r="H15">
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="H18">
         <v>1536</v>
       </c>
-      <c r="I15">
+      <c r="I18">
         <v>7.3020000000000003E-3</v>
       </c>
-      <c r="J15">
+      <c r="J18">
         <v>9.1159999999999993E-4</v>
       </c>
-      <c r="K15">
+      <c r="K18">
         <v>91834.754220799994</v>
       </c>
-      <c r="L15">
+      <c r="L18">
         <v>2.9000000000000005E-2</v>
       </c>
-      <c r="S15">
+      <c r="S18">
         <v>1536</v>
       </c>
-      <c r="T15">
+      <c r="T18">
         <v>5.9132300000000006E-2</v>
       </c>
-      <c r="U15">
+      <c r="U18">
         <v>2.4380000000000002E-4</v>
       </c>
-      <c r="V15">
+      <c r="V18">
         <v>93837.239220600008</v>
       </c>
-      <c r="W15">
-        <v>0</v>
-      </c>
-      <c r="Y15">
+      <c r="W18">
+        <v>0</v>
+      </c>
+      <c r="Y18">
         <v>1536</v>
       </c>
-      <c r="Z15">
+      <c r="Z18">
         <v>7.2446000000000012E-3</v>
       </c>
-      <c r="AA15">
+      <c r="AA18">
         <v>9.029000000000001E-4</v>
       </c>
-      <c r="AB15">
+      <c r="AB18">
         <v>91842.884035600015</v>
       </c>
-      <c r="AC15">
+      <c r="AC18">
         <v>3.2999999999999995E-2</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="B2:F2"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="S2:W2"/>
-    <mergeCell ref="Y2:AC2"/>
+  <mergeCells count="6">
+    <mergeCell ref="B2:O3"/>
+    <mergeCell ref="T2:AG3"/>
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="H5:L5"/>
+    <mergeCell ref="S5:W5"/>
+    <mergeCell ref="Y5:AC5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>

--- a/04-Development-and-Quality-Assurance/Evaluation-Testing/Logs/Kali/Kali_Data.xlsx
+++ b/04-Development-and-Quality-Assurance/Evaluation-Testing/Logs/Kali/Kali_Data.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29415"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -19,8 +19,11 @@
     <sheet name="IPv6 - TCP" sheetId="3" r:id="rId4"/>
     <sheet name="IPv6 - UDP" sheetId="4" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -38,6 +41,51 @@
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="526" uniqueCount="39">
+  <si>
+    <t>IPv4</t>
+  </si>
+  <si>
+    <t>IPv6</t>
+  </si>
+  <si>
+    <t>IPv4 TCP</t>
+  </si>
+  <si>
+    <t>IPv4 UDP</t>
+  </si>
+  <si>
+    <t>IPv6 TCP</t>
+  </si>
+  <si>
+    <t>IPv6 UDP</t>
+  </si>
+  <si>
+    <t>Packet Size</t>
+  </si>
+  <si>
+    <t>TCP Average Delay</t>
+  </si>
+  <si>
+    <t>TCP Jitter</t>
+  </si>
+  <si>
+    <t>TCP Bitrate</t>
+  </si>
+  <si>
+    <t>TCP Packet Loss</t>
+  </si>
+  <si>
+    <t>UDP Average Delay</t>
+  </si>
+  <si>
+    <t>UDP Jitter</t>
+  </si>
+  <si>
+    <t>UDP Bitrate</t>
+  </si>
+  <si>
+    <t>UDP Packet Loss</t>
+  </si>
   <si>
     <t>128</t>
   </si>
@@ -67,9 +115,6 @@
   </si>
   <si>
     <t>Average packet rate (pkt/s)</t>
-  </si>
-  <si>
-    <t>Packet Size</t>
   </si>
   <si>
     <t>Average Delay</t>
@@ -113,54 +158,12 @@
   <si>
     <t>1536</t>
   </si>
-  <si>
-    <t>TCP Average Delay</t>
-  </si>
-  <si>
-    <t>TCP Jitter</t>
-  </si>
-  <si>
-    <t>TCP Bitrate</t>
-  </si>
-  <si>
-    <t>TCP Packet Loss</t>
-  </si>
-  <si>
-    <t>UDP Average Delay</t>
-  </si>
-  <si>
-    <t>UDP Jitter</t>
-  </si>
-  <si>
-    <t>UDP Bitrate</t>
-  </si>
-  <si>
-    <t>UDP Packet Loss</t>
-  </si>
-  <si>
-    <t>IPv4 TCP</t>
-  </si>
-  <si>
-    <t>IPv4 UDP</t>
-  </si>
-  <si>
-    <t>IPv6 TCP</t>
-  </si>
-  <si>
-    <t>IPv6 UDP</t>
-  </si>
-  <si>
-    <t>IPv4</t>
-  </si>
-  <si>
-    <t>IPv6</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -210,13 +213,13 @@
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -9518,14 +9521,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{241AF353-C3A0-40A6-A389-2EE7141C0FF3}">
   <dimension ref="B2:AG18"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="17" max="18" width="9.140625" style="3"/>
+    <col min="17" max="18" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:33" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:33">
       <c r="B2" s="2" t="s">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -9541,7 +9544,7 @@
       <c r="N2" s="2"/>
       <c r="O2" s="2"/>
       <c r="T2" s="2" t="s">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="U2" s="2"/>
       <c r="V2" s="2"/>
@@ -9557,7 +9560,7 @@
       <c r="AF2" s="2"/>
       <c r="AG2" s="2"/>
     </row>
-    <row r="3" spans="2:33" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:33">
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
@@ -9587,99 +9590,99 @@
       <c r="AF3" s="2"/>
       <c r="AG3" s="2"/>
     </row>
-    <row r="5" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="H5" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
-      <c r="K5" s="1"/>
-      <c r="L5" s="1"/>
-      <c r="S5" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="T5" s="1"/>
-      <c r="U5" s="1"/>
-      <c r="V5" s="1"/>
-      <c r="W5" s="1"/>
-      <c r="Y5" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z5" s="1"/>
-      <c r="AA5" s="1"/>
-      <c r="AB5" s="1"/>
-      <c r="AC5" s="1"/>
-    </row>
-    <row r="6" spans="2:33" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:33" ht="15" customHeight="1">
+      <c r="B5" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="H5" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I5" s="3"/>
+      <c r="J5" s="3"/>
+      <c r="K5" s="3"/>
+      <c r="L5" s="3"/>
+      <c r="S5" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T5" s="3"/>
+      <c r="U5" s="3"/>
+      <c r="V5" s="3"/>
+      <c r="W5" s="3"/>
+      <c r="Y5" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z5" s="3"/>
+      <c r="AA5" s="3"/>
+      <c r="AB5" s="3"/>
+      <c r="AC5" s="3"/>
+    </row>
+    <row r="6" spans="2:33">
       <c r="B6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" t="s">
         <v>10</v>
       </c>
-      <c r="C6" t="s">
-        <v>25</v>
-      </c>
-      <c r="D6" t="s">
-        <v>26</v>
-      </c>
-      <c r="E6" t="s">
-        <v>27</v>
-      </c>
-      <c r="F6" t="s">
-        <v>28</v>
-      </c>
       <c r="H6" t="s">
+        <v>6</v>
+      </c>
+      <c r="I6" t="s">
+        <v>11</v>
+      </c>
+      <c r="J6" t="s">
+        <v>12</v>
+      </c>
+      <c r="K6" t="s">
+        <v>13</v>
+      </c>
+      <c r="L6" t="s">
+        <v>14</v>
+      </c>
+      <c r="S6" t="s">
+        <v>6</v>
+      </c>
+      <c r="T6" t="s">
+        <v>7</v>
+      </c>
+      <c r="U6" t="s">
+        <v>8</v>
+      </c>
+      <c r="V6" t="s">
+        <v>9</v>
+      </c>
+      <c r="W6" t="s">
         <v>10</v>
       </c>
-      <c r="I6" t="s">
-        <v>29</v>
-      </c>
-      <c r="J6" t="s">
-        <v>30</v>
-      </c>
-      <c r="K6" t="s">
-        <v>31</v>
-      </c>
-      <c r="L6" t="s">
-        <v>32</v>
-      </c>
-      <c r="S6" t="s">
-        <v>10</v>
-      </c>
-      <c r="T6" t="s">
-        <v>25</v>
-      </c>
-      <c r="U6" t="s">
-        <v>26</v>
-      </c>
-      <c r="V6" t="s">
-        <v>27</v>
-      </c>
-      <c r="W6" t="s">
-        <v>28</v>
-      </c>
       <c r="Y6" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Z6" t="s">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="AA6" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="AB6" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="AC6" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="7" spans="2:33" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="2:33">
       <c r="B7">
         <v>128</v>
       </c>
@@ -9741,7 +9744,7 @@
         <v>5.2000000000000005E-2</v>
       </c>
     </row>
-    <row r="8" spans="2:33" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:33">
       <c r="B8">
         <v>256</v>
       </c>
@@ -9803,7 +9806,7 @@
         <v>6.4000000000000015E-2</v>
       </c>
     </row>
-    <row r="9" spans="2:33" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:33">
       <c r="B9">
         <v>384</v>
       </c>
@@ -9865,7 +9868,7 @@
         <v>5.6000000000000008E-2</v>
       </c>
     </row>
-    <row r="10" spans="2:33" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:33">
       <c r="B10">
         <v>512</v>
       </c>
@@ -9927,7 +9930,7 @@
         <v>5.3000000000000005E-2</v>
       </c>
     </row>
-    <row r="11" spans="2:33" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:33">
       <c r="B11">
         <v>640</v>
       </c>
@@ -9989,7 +9992,7 @@
         <v>0.11899999999999999</v>
       </c>
     </row>
-    <row r="12" spans="2:33" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:33">
       <c r="B12">
         <v>768</v>
       </c>
@@ -10051,7 +10054,7 @@
         <v>6.0000000000000012E-2</v>
       </c>
     </row>
-    <row r="13" spans="2:33" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:33">
       <c r="B13">
         <v>896</v>
       </c>
@@ -10113,7 +10116,7 @@
         <v>4.9999999999999996E-2</v>
       </c>
     </row>
-    <row r="14" spans="2:33" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:33">
       <c r="B14">
         <v>1024</v>
       </c>
@@ -10175,7 +10178,7 @@
         <v>9.2999999999999985E-2</v>
       </c>
     </row>
-    <row r="15" spans="2:33" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:33">
       <c r="B15">
         <v>1152</v>
       </c>
@@ -10237,7 +10240,7 @@
         <v>5.2000000000000005E-2</v>
       </c>
     </row>
-    <row r="16" spans="2:33" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:33">
       <c r="B16">
         <v>1280</v>
       </c>
@@ -10299,7 +10302,7 @@
         <v>3.7999999999999992E-2</v>
       </c>
     </row>
-    <row r="17" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:29">
       <c r="B17">
         <v>1408</v>
       </c>
@@ -10361,7 +10364,7 @@
         <v>0.14499999999999996</v>
       </c>
     </row>
-    <row r="18" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:29">
       <c r="B18">
         <v>1536</v>
       </c>
@@ -10440,82 +10443,82 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A2:Z89"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:26">
       <c r="A2" t="s">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="L2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:26">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D3" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L3" t="s">
+        <v>17</v>
+      </c>
+      <c r="M3" t="s">
+        <v>18</v>
+      </c>
+      <c r="N3" t="s">
+        <v>19</v>
+      </c>
+      <c r="O3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>22</v>
+      </c>
+      <c r="R3" t="s">
+        <v>23</v>
+      </c>
+      <c r="S3" t="s">
+        <v>24</v>
+      </c>
+      <c r="V3" t="s">
         <v>6</v>
       </c>
-      <c r="F3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H3" t="s">
-        <v>9</v>
-      </c>
-      <c r="L3" t="s">
-        <v>2</v>
-      </c>
-      <c r="M3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P3" t="s">
-        <v>6</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>7</v>
-      </c>
-      <c r="R3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S3" t="s">
-        <v>9</v>
-      </c>
-      <c r="V3" t="s">
-        <v>10</v>
-      </c>
       <c r="W3" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="X3" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="Y3" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="Z3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:26">
       <c r="A4">
         <v>1</v>
       </c>
@@ -10584,7 +10587,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:26">
       <c r="A5">
         <v>5</v>
       </c>
@@ -10653,7 +10656,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:26">
       <c r="A6">
         <v>6</v>
       </c>
@@ -10722,7 +10725,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:26">
       <c r="A7">
         <v>4</v>
       </c>
@@ -10791,7 +10794,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:26">
       <c r="A8">
         <v>2</v>
       </c>
@@ -10860,7 +10863,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:26">
       <c r="A9">
         <v>7</v>
       </c>
@@ -10929,7 +10932,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:26">
       <c r="A10">
         <v>3</v>
       </c>
@@ -10998,7 +11001,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:26">
       <c r="A11">
         <v>9</v>
       </c>
@@ -11067,7 +11070,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:26">
       <c r="A12">
         <v>8</v>
       </c>
@@ -11136,7 +11139,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:26">
       <c r="A13">
         <v>10</v>
       </c>
@@ -11205,9 +11208,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:26">
       <c r="A14" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="B14">
         <f t="shared" ref="B14:H14" si="0">AVERAGE(B4:B13)</f>
@@ -11238,7 +11241,7 @@
         <v>16841.621274500001</v>
       </c>
       <c r="L14" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="M14">
         <f t="shared" ref="M14:S14" si="1">AVERAGE(M4:M13)</f>
@@ -11288,7 +11291,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:26">
       <c r="V15">
         <v>1536</v>
       </c>
@@ -11309,65 +11312,65 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:19">
       <c r="A17" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="L17" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19">
       <c r="A18" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="C18" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D18" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E18" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="F18" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="G18" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="H18" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="L18" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="M18" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="N18" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="O18" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="P18" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="Q18" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="R18" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="S18" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19">
       <c r="A19">
         <v>1</v>
       </c>
@@ -11417,7 +11420,7 @@
         <v>11437.488499999999</v>
       </c>
     </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:19">
       <c r="A20">
         <v>2</v>
       </c>
@@ -11467,7 +11470,7 @@
         <v>11437.176522</v>
       </c>
     </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:19">
       <c r="A21">
         <v>4</v>
       </c>
@@ -11517,7 +11520,7 @@
         <v>11423.810401999999</v>
       </c>
     </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:19">
       <c r="A22">
         <v>5</v>
       </c>
@@ -11567,7 +11570,7 @@
         <v>11440.200859</v>
       </c>
     </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:19">
       <c r="A23">
         <v>7</v>
       </c>
@@ -11617,7 +11620,7 @@
         <v>11443.438582000001</v>
       </c>
     </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:19">
       <c r="A24">
         <v>3</v>
       </c>
@@ -11667,7 +11670,7 @@
         <v>11429.482352999999</v>
       </c>
     </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:19">
       <c r="A25">
         <v>8</v>
       </c>
@@ -11717,7 +11720,7 @@
         <v>11417.914113999999</v>
       </c>
     </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:19">
       <c r="A26">
         <v>10</v>
       </c>
@@ -11767,7 +11770,7 @@
         <v>11424.552474</v>
       </c>
     </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:19">
       <c r="A27">
         <v>6</v>
       </c>
@@ -11817,7 +11820,7 @@
         <v>11430.037428</v>
       </c>
     </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:19">
       <c r="A28">
         <v>9</v>
       </c>
@@ -11867,9 +11870,9 @@
         <v>11411.785556999999</v>
       </c>
     </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:19">
       <c r="A29" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="B29">
         <f t="shared" ref="B29:H29" si="2">AVERAGE(B19:B28)</f>
@@ -11900,7 +11903,7 @@
         <v>16994.297857199999</v>
       </c>
       <c r="L29" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="M29">
         <f t="shared" ref="M29:S29" si="3">AVERAGE(M19:M28)</f>
@@ -11931,65 +11934,65 @@
         <v>11429.588679099999</v>
       </c>
     </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:19">
       <c r="A32" t="s">
+        <v>31</v>
+      </c>
+      <c r="L32" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19">
+      <c r="A33" t="s">
         <v>17</v>
       </c>
-      <c r="L32" t="s">
+      <c r="B33" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>2</v>
-      </c>
-      <c r="B33" t="s">
-        <v>3</v>
-      </c>
       <c r="C33" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D33" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E33" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="F33" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="G33" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="H33" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="L33" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="M33" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="N33" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="O33" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="P33" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="Q33" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="R33" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="S33" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19">
       <c r="A34">
         <v>1</v>
       </c>
@@ -12039,7 +12042,7 @@
         <v>10182.127721999999</v>
       </c>
     </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:19">
       <c r="A35">
         <v>4</v>
       </c>
@@ -12089,7 +12092,7 @@
         <v>10173.90697</v>
       </c>
     </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:19">
       <c r="A36">
         <v>5</v>
       </c>
@@ -12139,7 +12142,7 @@
         <v>10165.794486000001</v>
       </c>
     </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:19">
       <c r="A37">
         <v>2</v>
       </c>
@@ -12189,7 +12192,7 @@
         <v>10169.616935</v>
       </c>
     </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:19">
       <c r="A38">
         <v>3</v>
       </c>
@@ -12239,7 +12242,7 @@
         <v>10156.555289</v>
       </c>
     </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:19">
       <c r="A39">
         <v>6</v>
       </c>
@@ -12289,7 +12292,7 @@
         <v>10158.587622999999</v>
       </c>
     </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:19">
       <c r="A40">
         <v>8</v>
       </c>
@@ -12339,7 +12342,7 @@
         <v>10152.478897000001</v>
       </c>
     </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:19">
       <c r="A41">
         <v>7</v>
       </c>
@@ -12389,7 +12392,7 @@
         <v>10147.219692000001</v>
       </c>
     </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:19">
       <c r="A42">
         <v>9</v>
       </c>
@@ -12439,7 +12442,7 @@
         <v>10155.249787999999</v>
       </c>
     </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:19">
       <c r="A43">
         <v>10</v>
       </c>
@@ -12489,9 +12492,9 @@
         <v>10148.869237000001</v>
       </c>
     </row>
-    <row r="44" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:19">
       <c r="A44" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="B44">
         <f t="shared" ref="B44:H44" si="4">AVERAGE(B34:B43)</f>
@@ -12522,7 +12525,7 @@
         <v>17122.723129799997</v>
       </c>
       <c r="L44" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="M44">
         <f t="shared" ref="M44:S44" si="5">AVERAGE(M34:M43)</f>
@@ -12553,65 +12556,65 @@
         <v>10161.040663899999</v>
       </c>
     </row>
-    <row r="47" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:19">
       <c r="A47" t="s">
+        <v>33</v>
+      </c>
+      <c r="L47" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="48" spans="1:19">
+      <c r="A48" t="s">
+        <v>17</v>
+      </c>
+      <c r="B48" t="s">
+        <v>18</v>
+      </c>
+      <c r="C48" t="s">
         <v>19</v>
       </c>
-      <c r="L47" t="s">
+      <c r="D48" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="48" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>2</v>
-      </c>
-      <c r="B48" t="s">
-        <v>3</v>
-      </c>
-      <c r="C48" t="s">
-        <v>4</v>
-      </c>
-      <c r="D48" t="s">
-        <v>5</v>
-      </c>
       <c r="E48" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="F48" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="G48" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="H48" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="L48" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="M48" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="N48" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="O48" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="P48" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="Q48" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="R48" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="S48" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="49" spans="1:19" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="49" spans="1:19">
       <c r="A49">
         <v>4</v>
       </c>
@@ -12661,7 +12664,7 @@
         <v>9173.1401509999996</v>
       </c>
     </row>
-    <row r="50" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:19">
       <c r="A50">
         <v>2</v>
       </c>
@@ -12711,7 +12714,7 @@
         <v>9170.4162909999995</v>
       </c>
     </row>
-    <row r="51" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:19">
       <c r="A51">
         <v>1</v>
       </c>
@@ -12761,7 +12764,7 @@
         <v>9149.1204830000006</v>
       </c>
     </row>
-    <row r="52" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:19">
       <c r="A52">
         <v>5</v>
       </c>
@@ -12811,7 +12814,7 @@
         <v>9142.1753289999997</v>
       </c>
     </row>
-    <row r="53" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:19">
       <c r="A53">
         <v>3</v>
       </c>
@@ -12861,7 +12864,7 @@
         <v>9137.7128830000001</v>
       </c>
     </row>
-    <row r="54" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:19">
       <c r="A54">
         <v>6</v>
       </c>
@@ -12911,7 +12914,7 @@
         <v>9133.5580040000004</v>
       </c>
     </row>
-    <row r="55" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:19">
       <c r="A55">
         <v>8</v>
       </c>
@@ -12961,7 +12964,7 @@
         <v>9132.2561999999998</v>
       </c>
     </row>
-    <row r="56" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:19">
       <c r="A56">
         <v>10</v>
       </c>
@@ -13011,7 +13014,7 @@
         <v>9138.2613120000005</v>
       </c>
     </row>
-    <row r="57" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:19">
       <c r="A57">
         <v>7</v>
       </c>
@@ -13061,7 +13064,7 @@
         <v>9129.4734000000008</v>
       </c>
     </row>
-    <row r="58" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:19">
       <c r="A58">
         <v>9</v>
       </c>
@@ -13111,9 +13114,9 @@
         <v>9153.3205809999999</v>
       </c>
     </row>
-    <row r="59" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:19">
       <c r="A59" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="B59">
         <f t="shared" ref="B59:H59" si="6">AVERAGE(B49:B58)</f>
@@ -13144,7 +13147,7 @@
         <v>17110.233019200001</v>
       </c>
       <c r="L59" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="M59">
         <f t="shared" ref="M59:S59" si="7">AVERAGE(M49:M58)</f>
@@ -13175,65 +13178,65 @@
         <v>9145.9434634000008</v>
       </c>
     </row>
-    <row r="62" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:19">
       <c r="A62" t="s">
+        <v>35</v>
+      </c>
+      <c r="L62" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="63" spans="1:19">
+      <c r="A63" t="s">
+        <v>17</v>
+      </c>
+      <c r="B63" t="s">
+        <v>18</v>
+      </c>
+      <c r="C63" t="s">
+        <v>19</v>
+      </c>
+      <c r="D63" t="s">
+        <v>20</v>
+      </c>
+      <c r="E63" t="s">
         <v>21</v>
       </c>
-      <c r="L62" t="s">
+      <c r="F63" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="63" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
-        <v>2</v>
-      </c>
-      <c r="B63" t="s">
-        <v>3</v>
-      </c>
-      <c r="C63" t="s">
-        <v>4</v>
-      </c>
-      <c r="D63" t="s">
-        <v>5</v>
-      </c>
-      <c r="E63" t="s">
-        <v>6</v>
-      </c>
-      <c r="F63" t="s">
-        <v>7</v>
-      </c>
       <c r="G63" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="H63" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="L63" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="M63" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="N63" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="O63" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="P63" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="Q63" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="R63" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="S63" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="64" spans="1:19" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="64" spans="1:19">
       <c r="A64">
         <v>1</v>
       </c>
@@ -13283,7 +13286,7 @@
         <v>8345.6441419999992</v>
       </c>
     </row>
-    <row r="65" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:19">
       <c r="A65">
         <v>5</v>
       </c>
@@ -13333,7 +13336,7 @@
         <v>8345.425389</v>
       </c>
     </row>
-    <row r="66" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:19">
       <c r="A66">
         <v>6</v>
       </c>
@@ -13383,7 +13386,7 @@
         <v>8318.1094759999996</v>
       </c>
     </row>
-    <row r="67" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:19">
       <c r="A67">
         <v>3</v>
       </c>
@@ -13433,7 +13436,7 @@
         <v>8334.9121219999997</v>
       </c>
     </row>
-    <row r="68" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:19">
       <c r="A68">
         <v>4</v>
       </c>
@@ -13483,7 +13486,7 @@
         <v>8305.7881880000004</v>
       </c>
     </row>
-    <row r="69" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:19">
       <c r="A69">
         <v>2</v>
       </c>
@@ -13533,7 +13536,7 @@
         <v>8304.071457</v>
       </c>
     </row>
-    <row r="70" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:19">
       <c r="A70">
         <v>7</v>
       </c>
@@ -13583,7 +13586,7 @@
         <v>8304.9916580000008</v>
       </c>
     </row>
-    <row r="71" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:19">
       <c r="A71">
         <v>8</v>
       </c>
@@ -13633,7 +13636,7 @@
         <v>8310.4582030000001</v>
       </c>
     </row>
-    <row r="72" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:19">
       <c r="A72">
         <v>9</v>
       </c>
@@ -13683,7 +13686,7 @@
         <v>8305.2405909999998</v>
       </c>
     </row>
-    <row r="73" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:19">
       <c r="A73">
         <v>10</v>
       </c>
@@ -13733,9 +13736,9 @@
         <v>8315.0886759999994</v>
       </c>
     </row>
-    <row r="74" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:19">
       <c r="A74" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="B74">
         <f t="shared" ref="B74:H74" si="8">AVERAGE(B64:B73)</f>
@@ -13766,7 +13769,7 @@
         <v>17167.358882699999</v>
       </c>
       <c r="L74" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="M74">
         <f t="shared" ref="M74:S74" si="9">AVERAGE(M64:M73)</f>
@@ -13797,65 +13800,65 @@
         <v>8318.9729901999999</v>
       </c>
     </row>
-    <row r="77" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:19">
       <c r="A77" t="s">
+        <v>37</v>
+      </c>
+      <c r="L77" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="78" spans="1:19">
+      <c r="A78" t="s">
+        <v>17</v>
+      </c>
+      <c r="B78" t="s">
+        <v>18</v>
+      </c>
+      <c r="C78" t="s">
+        <v>19</v>
+      </c>
+      <c r="D78" t="s">
+        <v>20</v>
+      </c>
+      <c r="E78" t="s">
+        <v>21</v>
+      </c>
+      <c r="F78" t="s">
+        <v>22</v>
+      </c>
+      <c r="G78" t="s">
         <v>23</v>
       </c>
-      <c r="L77" t="s">
+      <c r="H78" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="78" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
-        <v>2</v>
-      </c>
-      <c r="B78" t="s">
-        <v>3</v>
-      </c>
-      <c r="C78" t="s">
-        <v>4</v>
-      </c>
-      <c r="D78" t="s">
-        <v>5</v>
-      </c>
-      <c r="E78" t="s">
-        <v>6</v>
-      </c>
-      <c r="F78" t="s">
-        <v>7</v>
-      </c>
-      <c r="G78" t="s">
-        <v>8</v>
-      </c>
-      <c r="H78" t="s">
-        <v>9</v>
-      </c>
       <c r="L78" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="M78" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="N78" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="O78" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="P78" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="Q78" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="R78" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="S78" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="79" spans="1:19" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="79" spans="1:19">
       <c r="A79">
         <v>1</v>
       </c>
@@ -13905,7 +13908,7 @@
         <v>7660.024942</v>
       </c>
     </row>
-    <row r="80" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:19">
       <c r="A80">
         <v>5</v>
       </c>
@@ -13955,7 +13958,7 @@
         <v>7656.2799409999998</v>
       </c>
     </row>
-    <row r="81" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:19">
       <c r="A81">
         <v>6</v>
       </c>
@@ -14005,7 +14008,7 @@
         <v>7622.9332400000003</v>
       </c>
     </row>
-    <row r="82" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:19">
       <c r="A82">
         <v>2</v>
       </c>
@@ -14055,7 +14058,7 @@
         <v>7615.3007260000004</v>
       </c>
     </row>
-    <row r="83" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:19">
       <c r="A83">
         <v>4</v>
       </c>
@@ -14105,7 +14108,7 @@
         <v>7618.7244689999998</v>
       </c>
     </row>
-    <row r="84" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:19">
       <c r="A84">
         <v>3</v>
       </c>
@@ -14155,7 +14158,7 @@
         <v>7624.3610859999999</v>
       </c>
     </row>
-    <row r="85" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:19">
       <c r="A85">
         <v>7</v>
       </c>
@@ -14205,7 +14208,7 @@
         <v>7610.439875</v>
       </c>
     </row>
-    <row r="86" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:19">
       <c r="A86">
         <v>8</v>
       </c>
@@ -14255,7 +14258,7 @@
         <v>7628.9479170000004</v>
       </c>
     </row>
-    <row r="87" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:19">
       <c r="A87">
         <v>9</v>
       </c>
@@ -14305,7 +14308,7 @@
         <v>7632.8917270000002</v>
       </c>
     </row>
-    <row r="88" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:19">
       <c r="A88">
         <v>10</v>
       </c>
@@ -14355,9 +14358,9 @@
         <v>7620.395219</v>
       </c>
     </row>
-    <row r="89" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:19">
       <c r="A89" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="B89">
         <f t="shared" ref="B89:H89" si="10">AVERAGE(B79:B88)</f>
@@ -14388,7 +14391,7 @@
         <v>15231.3786937</v>
       </c>
       <c r="L89" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="M89">
         <f t="shared" ref="M89:S89" si="11">AVERAGE(M79:M88)</f>
@@ -14427,82 +14430,82 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A2:Z89"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:26">
       <c r="A2" t="s">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="L2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:26">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D3" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L3" t="s">
+        <v>17</v>
+      </c>
+      <c r="M3" t="s">
+        <v>18</v>
+      </c>
+      <c r="N3" t="s">
+        <v>19</v>
+      </c>
+      <c r="O3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>22</v>
+      </c>
+      <c r="R3" t="s">
+        <v>23</v>
+      </c>
+      <c r="S3" t="s">
+        <v>24</v>
+      </c>
+      <c r="V3" t="s">
         <v>6</v>
       </c>
-      <c r="F3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H3" t="s">
-        <v>9</v>
-      </c>
-      <c r="L3" t="s">
-        <v>2</v>
-      </c>
-      <c r="M3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P3" t="s">
-        <v>6</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>7</v>
-      </c>
-      <c r="R3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S3" t="s">
-        <v>9</v>
-      </c>
-      <c r="V3" t="s">
-        <v>10</v>
-      </c>
       <c r="W3" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="X3" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="Y3" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="Z3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:26">
       <c r="A4">
         <v>5</v>
       </c>
@@ -14571,7 +14574,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:26">
       <c r="A5">
         <v>3</v>
       </c>
@@ -14640,7 +14643,7 @@
         <v>6.0000000000000012E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:26">
       <c r="A6">
         <v>2</v>
       </c>
@@ -14709,7 +14712,7 @@
         <v>6.0000000000000012E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:26">
       <c r="A7">
         <v>1</v>
       </c>
@@ -14778,7 +14781,7 @@
         <v>0.10800000000000001</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:26">
       <c r="A8">
         <v>6</v>
       </c>
@@ -14847,7 +14850,7 @@
         <v>5.2000000000000005E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:26">
       <c r="A9">
         <v>4</v>
       </c>
@@ -14916,7 +14919,7 @@
         <v>4.9999999999999996E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:26">
       <c r="A10">
         <v>8</v>
       </c>
@@ -14985,7 +14988,7 @@
         <v>9.9999999999999992E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:26">
       <c r="A11">
         <v>7</v>
       </c>
@@ -15054,7 +15057,7 @@
         <v>4.6999999999999993E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:26">
       <c r="A12">
         <v>10</v>
       </c>
@@ -15123,7 +15126,7 @@
         <v>8.299999999999999E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:26">
       <c r="A13">
         <v>9</v>
       </c>
@@ -15192,9 +15195,9 @@
         <v>1.8999999999999996E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:26">
       <c r="A14" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="B14">
         <f t="shared" ref="B14:H14" si="0">AVERAGE(B4:B13)</f>
@@ -15225,7 +15228,7 @@
         <v>17047.786803999999</v>
       </c>
       <c r="L14" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="M14">
         <f t="shared" ref="M14:S14" si="1">AVERAGE(M4:M13)</f>
@@ -15275,7 +15278,7 @@
         <v>0.217</v>
       </c>
     </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:26">
       <c r="V15">
         <v>1536</v>
       </c>
@@ -15296,65 +15299,65 @@
         <v>2.9000000000000005E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:19">
       <c r="A17" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="L17" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19">
       <c r="A18" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="C18" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D18" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E18" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="F18" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="G18" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="H18" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="L18" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="M18" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="N18" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="O18" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="P18" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="Q18" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="R18" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="S18" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19">
       <c r="A19">
         <v>1</v>
       </c>
@@ -15404,7 +15407,7 @@
         <v>11410.978843000001</v>
       </c>
     </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:19">
       <c r="A20">
         <v>2</v>
       </c>
@@ -15454,7 +15457,7 @@
         <v>11409.509534000001</v>
       </c>
     </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:19">
       <c r="A21">
         <v>4</v>
       </c>
@@ -15504,7 +15507,7 @@
         <v>11383.943696</v>
       </c>
     </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:19">
       <c r="A22">
         <v>6</v>
       </c>
@@ -15554,7 +15557,7 @@
         <v>11382.617661</v>
       </c>
     </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:19">
       <c r="A23">
         <v>9</v>
       </c>
@@ -15604,7 +15607,7 @@
         <v>11381.867243999999</v>
       </c>
     </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:19">
       <c r="A24">
         <v>8</v>
       </c>
@@ -15654,7 +15657,7 @@
         <v>11382.702191</v>
       </c>
     </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:19">
       <c r="A25">
         <v>10</v>
       </c>
@@ -15704,7 +15707,7 @@
         <v>11382.507299999999</v>
       </c>
     </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:19">
       <c r="A26">
         <v>7</v>
       </c>
@@ -15754,7 +15757,7 @@
         <v>11382.159657</v>
       </c>
     </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:19">
       <c r="A27">
         <v>5</v>
       </c>
@@ -15804,7 +15807,7 @@
         <v>11385.566692</v>
       </c>
     </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:19">
       <c r="A28">
         <v>3</v>
       </c>
@@ -15854,9 +15857,9 @@
         <v>11382.684594</v>
       </c>
     </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:19">
       <c r="A29" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="B29">
         <f t="shared" ref="B29:H29" si="2">AVERAGE(B19:B28)</f>
@@ -15887,7 +15890,7 @@
         <v>17061.826270900005</v>
       </c>
       <c r="L29" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="M29">
         <f t="shared" ref="M29:S29" si="3">AVERAGE(M19:M28)</f>
@@ -15918,65 +15921,65 @@
         <v>11388.453741199999</v>
       </c>
     </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:19">
       <c r="A32" t="s">
+        <v>31</v>
+      </c>
+      <c r="L32" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19">
+      <c r="A33" t="s">
         <v>17</v>
       </c>
-      <c r="L32" t="s">
+      <c r="B33" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>2</v>
-      </c>
-      <c r="B33" t="s">
-        <v>3</v>
-      </c>
       <c r="C33" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D33" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E33" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="F33" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="G33" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="H33" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="L33" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="M33" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="N33" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="O33" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="P33" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="Q33" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="R33" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="S33" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19">
       <c r="A34">
         <v>4</v>
       </c>
@@ -16026,7 +16029,7 @@
         <v>10232.565855000001</v>
       </c>
     </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:19">
       <c r="A35">
         <v>5</v>
       </c>
@@ -16076,7 +16079,7 @@
         <v>10233.918421</v>
       </c>
     </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:19">
       <c r="A36">
         <v>1</v>
       </c>
@@ -16126,7 +16129,7 @@
         <v>10190.95256</v>
       </c>
     </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:19">
       <c r="A37">
         <v>3</v>
       </c>
@@ -16176,7 +16179,7 @@
         <v>10190.739437</v>
       </c>
     </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:19">
       <c r="A38">
         <v>10</v>
       </c>
@@ -16226,7 +16229,7 @@
         <v>10190.686082</v>
       </c>
     </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:19">
       <c r="A39">
         <v>8</v>
       </c>
@@ -16276,7 +16279,7 @@
         <v>10190.768190000001</v>
       </c>
     </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:19">
       <c r="A40">
         <v>7</v>
       </c>
@@ -16326,7 +16329,7 @@
         <v>10191.364051</v>
       </c>
     </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:19">
       <c r="A41">
         <v>6</v>
       </c>
@@ -16376,7 +16379,7 @@
         <v>10191.183781</v>
       </c>
     </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:19">
       <c r="A42">
         <v>2</v>
       </c>
@@ -16426,7 +16429,7 @@
         <v>10190.047968000001</v>
       </c>
     </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:19">
       <c r="A43">
         <v>9</v>
       </c>
@@ -16476,9 +16479,9 @@
         <v>10191.298503</v>
       </c>
     </row>
-    <row r="44" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:19">
       <c r="A44" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="B44">
         <f t="shared" ref="B44:H44" si="4">AVERAGE(B34:B43)</f>
@@ -16509,7 +16512,7 @@
         <v>16977.401639299998</v>
       </c>
       <c r="L44" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="M44">
         <f t="shared" ref="M44:S44" si="5">AVERAGE(M34:M43)</f>
@@ -16540,65 +16543,65 @@
         <v>10199.3524848</v>
       </c>
     </row>
-    <row r="47" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:19">
       <c r="A47" t="s">
+        <v>33</v>
+      </c>
+      <c r="L47" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="48" spans="1:19">
+      <c r="A48" t="s">
+        <v>17</v>
+      </c>
+      <c r="B48" t="s">
+        <v>18</v>
+      </c>
+      <c r="C48" t="s">
         <v>19</v>
       </c>
-      <c r="L47" t="s">
+      <c r="D48" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="48" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>2</v>
-      </c>
-      <c r="B48" t="s">
-        <v>3</v>
-      </c>
-      <c r="C48" t="s">
-        <v>4</v>
-      </c>
-      <c r="D48" t="s">
-        <v>5</v>
-      </c>
       <c r="E48" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="F48" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="G48" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="H48" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="L48" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="M48" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="N48" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="O48" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="P48" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="Q48" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="R48" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="S48" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="49" spans="1:19" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="49" spans="1:19">
       <c r="A49">
         <v>5</v>
       </c>
@@ -16648,7 +16651,7 @@
         <v>9288.6120879999999</v>
       </c>
     </row>
-    <row r="50" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:19">
       <c r="A50">
         <v>3</v>
       </c>
@@ -16698,7 +16701,7 @@
         <v>9287.6893830000008</v>
       </c>
     </row>
-    <row r="51" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:19">
       <c r="A51">
         <v>6</v>
       </c>
@@ -16748,7 +16751,7 @@
         <v>9234.0266140000003</v>
       </c>
     </row>
-    <row r="52" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:19">
       <c r="A52">
         <v>9</v>
       </c>
@@ -16798,7 +16801,7 @@
         <v>9232.86312</v>
       </c>
     </row>
-    <row r="53" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:19">
       <c r="A53">
         <v>1</v>
       </c>
@@ -16848,7 +16851,7 @@
         <v>9232.7654640000001</v>
       </c>
     </row>
-    <row r="54" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:19">
       <c r="A54">
         <v>2</v>
       </c>
@@ -16898,7 +16901,7 @@
         <v>9233.6169860000009</v>
       </c>
     </row>
-    <row r="55" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:19">
       <c r="A55">
         <v>8</v>
       </c>
@@ -16948,7 +16951,7 @@
         <v>9232.598414</v>
       </c>
     </row>
-    <row r="56" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:19">
       <c r="A56">
         <v>4</v>
       </c>
@@ -16998,7 +17001,7 @@
         <v>9232.0529619999998</v>
       </c>
     </row>
-    <row r="57" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:19">
       <c r="A57">
         <v>10</v>
       </c>
@@ -17048,7 +17051,7 @@
         <v>9233.5592130000005</v>
       </c>
     </row>
-    <row r="58" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:19">
       <c r="A58">
         <v>7</v>
       </c>
@@ -17098,9 +17101,9 @@
         <v>9233.3030190000009</v>
       </c>
     </row>
-    <row r="59" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:19">
       <c r="A59" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="B59">
         <f t="shared" ref="B59:H59" si="6">AVERAGE(B49:B58)</f>
@@ -17131,7 +17134,7 @@
         <v>17040.288323099998</v>
       </c>
       <c r="L59" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="M59">
         <f t="shared" ref="M59:S59" si="7">AVERAGE(M49:M58)</f>
@@ -17162,65 +17165,65 @@
         <v>9244.1087263000009</v>
       </c>
     </row>
-    <row r="62" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:19">
       <c r="A62" t="s">
+        <v>35</v>
+      </c>
+      <c r="L62" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="63" spans="1:19">
+      <c r="A63" t="s">
+        <v>17</v>
+      </c>
+      <c r="B63" t="s">
+        <v>18</v>
+      </c>
+      <c r="C63" t="s">
+        <v>19</v>
+      </c>
+      <c r="D63" t="s">
+        <v>20</v>
+      </c>
+      <c r="E63" t="s">
         <v>21</v>
       </c>
-      <c r="L62" t="s">
+      <c r="F63" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="63" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
-        <v>2</v>
-      </c>
-      <c r="B63" t="s">
-        <v>3</v>
-      </c>
-      <c r="C63" t="s">
-        <v>4</v>
-      </c>
-      <c r="D63" t="s">
-        <v>5</v>
-      </c>
-      <c r="E63" t="s">
-        <v>6</v>
-      </c>
-      <c r="F63" t="s">
-        <v>7</v>
-      </c>
       <c r="G63" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="H63" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="L63" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="M63" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="N63" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="O63" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="P63" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="Q63" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="R63" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="S63" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="64" spans="1:19" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="64" spans="1:19">
       <c r="A64">
         <v>1</v>
       </c>
@@ -17270,7 +17273,7 @@
         <v>8489.7935369999996</v>
       </c>
     </row>
-    <row r="65" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:19">
       <c r="A65">
         <v>3</v>
       </c>
@@ -17320,7 +17323,7 @@
         <v>8487.9845079999996</v>
       </c>
     </row>
-    <row r="66" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:19">
       <c r="A66">
         <v>7</v>
       </c>
@@ -17370,7 +17373,7 @@
         <v>8425.8657349999994</v>
       </c>
     </row>
-    <row r="67" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:19">
       <c r="A67">
         <v>2</v>
       </c>
@@ -17420,7 +17423,7 @@
         <v>8425.0590830000001</v>
       </c>
     </row>
-    <row r="68" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:19">
       <c r="A68">
         <v>9</v>
       </c>
@@ -17470,7 +17473,7 @@
         <v>8425.4093680000005</v>
       </c>
     </row>
-    <row r="69" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:19">
       <c r="A69">
         <v>6</v>
       </c>
@@ -17520,7 +17523,7 @@
         <v>8424.8660990000008</v>
       </c>
     </row>
-    <row r="70" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:19">
       <c r="A70">
         <v>8</v>
       </c>
@@ -17570,7 +17573,7 @@
         <v>8424.8909239999994</v>
       </c>
     </row>
-    <row r="71" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:19">
       <c r="A71">
         <v>5</v>
       </c>
@@ -17620,7 +17623,7 @@
         <v>8425.2999290000007</v>
       </c>
     </row>
-    <row r="72" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:19">
       <c r="A72">
         <v>10</v>
       </c>
@@ -17670,7 +17673,7 @@
         <v>8424.4527139999991</v>
       </c>
     </row>
-    <row r="73" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:19">
       <c r="A73">
         <v>4</v>
       </c>
@@ -17720,9 +17723,9 @@
         <v>8424.6530559999992</v>
       </c>
     </row>
-    <row r="74" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:19">
       <c r="A74" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="B74">
         <f t="shared" ref="B74:H74" si="8">AVERAGE(B64:B73)</f>
@@ -17753,7 +17756,7 @@
         <v>16991.392938099998</v>
       </c>
       <c r="L74" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="M74">
         <f t="shared" ref="M74:S74" si="9">AVERAGE(M64:M73)</f>
@@ -17784,65 +17787,65 @@
         <v>8437.8274952999982</v>
       </c>
     </row>
-    <row r="77" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:19">
       <c r="A77" t="s">
+        <v>37</v>
+      </c>
+      <c r="L77" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="78" spans="1:19">
+      <c r="A78" t="s">
+        <v>17</v>
+      </c>
+      <c r="B78" t="s">
+        <v>18</v>
+      </c>
+      <c r="C78" t="s">
+        <v>19</v>
+      </c>
+      <c r="D78" t="s">
+        <v>20</v>
+      </c>
+      <c r="E78" t="s">
+        <v>21</v>
+      </c>
+      <c r="F78" t="s">
+        <v>22</v>
+      </c>
+      <c r="G78" t="s">
         <v>23</v>
       </c>
-      <c r="L77" t="s">
+      <c r="H78" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="78" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
-        <v>2</v>
-      </c>
-      <c r="B78" t="s">
-        <v>3</v>
-      </c>
-      <c r="C78" t="s">
-        <v>4</v>
-      </c>
-      <c r="D78" t="s">
-        <v>5</v>
-      </c>
-      <c r="E78" t="s">
-        <v>6</v>
-      </c>
-      <c r="F78" t="s">
-        <v>7</v>
-      </c>
-      <c r="G78" t="s">
-        <v>8</v>
-      </c>
-      <c r="H78" t="s">
-        <v>9</v>
-      </c>
       <c r="L78" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="M78" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="N78" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="O78" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="P78" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="Q78" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="R78" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="S78" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="79" spans="1:19" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="79" spans="1:19">
       <c r="A79">
         <v>1</v>
       </c>
@@ -17892,7 +17895,7 @@
         <v>7532.6444240000001</v>
       </c>
     </row>
-    <row r="80" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:19">
       <c r="A80">
         <v>2</v>
       </c>
@@ -17942,7 +17945,7 @@
         <v>7533.5137329999998</v>
       </c>
     </row>
-    <row r="81" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:19">
       <c r="A81">
         <v>5</v>
       </c>
@@ -17992,7 +17995,7 @@
         <v>7459.8437180000001</v>
       </c>
     </row>
-    <row r="82" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:19">
       <c r="A82">
         <v>6</v>
       </c>
@@ -18042,7 +18045,7 @@
         <v>7460.4998850000002</v>
       </c>
     </row>
-    <row r="83" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:19">
       <c r="A83">
         <v>10</v>
       </c>
@@ -18092,7 +18095,7 @@
         <v>7458.286814</v>
       </c>
     </row>
-    <row r="84" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:19">
       <c r="A84">
         <v>3</v>
       </c>
@@ -18142,7 +18145,7 @@
         <v>7457.752281</v>
       </c>
     </row>
-    <row r="85" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:19">
       <c r="A85">
         <v>4</v>
       </c>
@@ -18192,7 +18195,7 @@
         <v>7458.4830439999996</v>
       </c>
     </row>
-    <row r="86" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:19">
       <c r="A86">
         <v>9</v>
       </c>
@@ -18242,7 +18245,7 @@
         <v>7457.8445860000002</v>
       </c>
     </row>
-    <row r="87" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:19">
       <c r="A87">
         <v>7</v>
       </c>
@@ -18292,7 +18295,7 @@
         <v>7458.9997430000003</v>
       </c>
     </row>
-    <row r="88" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:19">
       <c r="A88">
         <v>8</v>
       </c>
@@ -18342,9 +18345,9 @@
         <v>7457.4460790000003</v>
       </c>
     </row>
-    <row r="89" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:19">
       <c r="A89" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="B89">
         <f t="shared" ref="B89:H89" si="10">AVERAGE(B79:B88)</f>
@@ -18375,7 +18378,7 @@
         <v>14826.116807099999</v>
       </c>
       <c r="L89" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="M89">
         <f t="shared" ref="M89:S89" si="11">AVERAGE(M79:M88)</f>
@@ -18414,82 +18417,82 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A2:Z89"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:26">
       <c r="A2" t="s">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="L2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:26">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D3" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L3" t="s">
+        <v>17</v>
+      </c>
+      <c r="M3" t="s">
+        <v>18</v>
+      </c>
+      <c r="N3" t="s">
+        <v>19</v>
+      </c>
+      <c r="O3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>22</v>
+      </c>
+      <c r="R3" t="s">
+        <v>23</v>
+      </c>
+      <c r="S3" t="s">
+        <v>24</v>
+      </c>
+      <c r="V3" t="s">
         <v>6</v>
       </c>
-      <c r="F3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H3" t="s">
-        <v>9</v>
-      </c>
-      <c r="L3" t="s">
-        <v>2</v>
-      </c>
-      <c r="M3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P3" t="s">
-        <v>6</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>7</v>
-      </c>
-      <c r="R3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S3" t="s">
-        <v>9</v>
-      </c>
-      <c r="V3" t="s">
-        <v>10</v>
-      </c>
       <c r="W3" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="X3" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="Y3" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="Z3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:26">
       <c r="A4">
         <v>4</v>
       </c>
@@ -18558,7 +18561,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:26">
       <c r="A5">
         <v>7</v>
       </c>
@@ -18627,7 +18630,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:26">
       <c r="A6">
         <v>6</v>
       </c>
@@ -18696,7 +18699,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:26">
       <c r="A7">
         <v>2</v>
       </c>
@@ -18765,7 +18768,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:26">
       <c r="A8">
         <v>5</v>
       </c>
@@ -18834,7 +18837,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:26">
       <c r="A9">
         <v>1</v>
       </c>
@@ -18903,7 +18906,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:26">
       <c r="A10">
         <v>3</v>
       </c>
@@ -18972,7 +18975,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:26">
       <c r="A11">
         <v>8</v>
       </c>
@@ -19041,7 +19044,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:26">
       <c r="A12">
         <v>10</v>
       </c>
@@ -19110,7 +19113,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:26">
       <c r="A13">
         <v>9</v>
       </c>
@@ -19179,9 +19182,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:26">
       <c r="A14" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="B14">
         <f t="shared" ref="B14:H14" si="0">AVERAGE(B4:B13)</f>
@@ -19212,7 +19215,7 @@
         <v>16857.2101778</v>
       </c>
       <c r="L14" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="M14">
         <f t="shared" ref="M14:S14" si="1">AVERAGE(M4:M13)</f>
@@ -19262,7 +19265,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:26">
       <c r="V15">
         <v>1536</v>
       </c>
@@ -19283,65 +19286,65 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:19">
       <c r="A17" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="L17" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19">
       <c r="A18" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="C18" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D18" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E18" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="F18" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="G18" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="H18" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="L18" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="M18" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="N18" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="O18" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="P18" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="Q18" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="R18" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="S18" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19">
       <c r="A19">
         <v>1</v>
       </c>
@@ -19391,7 +19394,7 @@
         <v>11436.350611</v>
       </c>
     </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:19">
       <c r="A20">
         <v>4</v>
       </c>
@@ -19441,7 +19444,7 @@
         <v>11437.521563</v>
       </c>
     </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:19">
       <c r="A21">
         <v>3</v>
       </c>
@@ -19491,7 +19494,7 @@
         <v>11417.202524</v>
       </c>
     </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:19">
       <c r="A22">
         <v>2</v>
       </c>
@@ -19541,7 +19544,7 @@
         <v>11418.715522</v>
       </c>
     </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:19">
       <c r="A23">
         <v>6</v>
       </c>
@@ -19591,7 +19594,7 @@
         <v>11448.950644</v>
       </c>
     </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:19">
       <c r="A24">
         <v>7</v>
       </c>
@@ -19641,7 +19644,7 @@
         <v>11433.753957999999</v>
       </c>
     </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:19">
       <c r="A25">
         <v>5</v>
       </c>
@@ -19691,7 +19694,7 @@
         <v>11438.148348999999</v>
       </c>
     </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:19">
       <c r="A26">
         <v>8</v>
       </c>
@@ -19741,7 +19744,7 @@
         <v>11416.656449</v>
       </c>
     </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:19">
       <c r="A27">
         <v>9</v>
       </c>
@@ -19791,7 +19794,7 @@
         <v>11410.273504999999</v>
       </c>
     </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:19">
       <c r="A28">
         <v>10</v>
       </c>
@@ -19841,9 +19844,9 @@
         <v>11436.227668</v>
       </c>
     </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:19">
       <c r="A29" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="B29">
         <f t="shared" ref="B29:H29" si="2">AVERAGE(B19:B28)</f>
@@ -19874,7 +19877,7 @@
         <v>17000.969324600002</v>
       </c>
       <c r="L29" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="M29">
         <f t="shared" ref="M29:S29" si="3">AVERAGE(M19:M28)</f>
@@ -19905,65 +19908,65 @@
         <v>11429.380079300001</v>
       </c>
     </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:19">
       <c r="A32" t="s">
+        <v>31</v>
+      </c>
+      <c r="L32" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19">
+      <c r="A33" t="s">
         <v>17</v>
       </c>
-      <c r="L32" t="s">
+      <c r="B33" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>2</v>
-      </c>
-      <c r="B33" t="s">
-        <v>3</v>
-      </c>
       <c r="C33" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D33" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E33" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="F33" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="G33" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="H33" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="L33" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="M33" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="N33" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="O33" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="P33" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="Q33" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="R33" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="S33" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19">
       <c r="A34">
         <v>4</v>
       </c>
@@ -20013,7 +20016,7 @@
         <v>10179.657278000001</v>
       </c>
     </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:19">
       <c r="A35">
         <v>3</v>
       </c>
@@ -20063,7 +20066,7 @@
         <v>10174.177682</v>
       </c>
     </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:19">
       <c r="A36">
         <v>1</v>
       </c>
@@ -20113,7 +20116,7 @@
         <v>10161.263704000001</v>
       </c>
     </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:19">
       <c r="A37">
         <v>5</v>
       </c>
@@ -20163,7 +20166,7 @@
         <v>10165.300877</v>
       </c>
     </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:19">
       <c r="A38">
         <v>7</v>
       </c>
@@ -20213,7 +20216,7 @@
         <v>10173.795727000001</v>
       </c>
     </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:19">
       <c r="A39">
         <v>8</v>
       </c>
@@ -20263,7 +20266,7 @@
         <v>10149.960950999999</v>
       </c>
     </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:19">
       <c r="A40">
         <v>2</v>
       </c>
@@ -20313,7 +20316,7 @@
         <v>10147.293974</v>
       </c>
     </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:19">
       <c r="A41">
         <v>6</v>
       </c>
@@ -20363,7 +20366,7 @@
         <v>10152.864798000001</v>
       </c>
     </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:19">
       <c r="A42">
         <v>10</v>
       </c>
@@ -20413,7 +20416,7 @@
         <v>10162.080629</v>
       </c>
     </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:19">
       <c r="A43">
         <v>9</v>
       </c>
@@ -20463,9 +20466,9 @@
         <v>10152.569528</v>
       </c>
     </row>
-    <row r="44" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:19">
       <c r="A44" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="B44">
         <f t="shared" ref="B44:H44" si="4">AVERAGE(B34:B43)</f>
@@ -20496,7 +20499,7 @@
         <v>17107.1072045</v>
       </c>
       <c r="L44" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="M44">
         <f t="shared" ref="M44:S44" si="5">AVERAGE(M34:M43)</f>
@@ -20527,65 +20530,65 @@
         <v>10161.896514799999</v>
       </c>
     </row>
-    <row r="47" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:19">
       <c r="A47" t="s">
+        <v>33</v>
+      </c>
+      <c r="L47" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="48" spans="1:19">
+      <c r="A48" t="s">
+        <v>17</v>
+      </c>
+      <c r="B48" t="s">
+        <v>18</v>
+      </c>
+      <c r="C48" t="s">
         <v>19</v>
       </c>
-      <c r="L47" t="s">
+      <c r="D48" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="48" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>2</v>
-      </c>
-      <c r="B48" t="s">
-        <v>3</v>
-      </c>
-      <c r="C48" t="s">
-        <v>4</v>
-      </c>
-      <c r="D48" t="s">
-        <v>5</v>
-      </c>
       <c r="E48" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="F48" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="G48" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="H48" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="L48" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="M48" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="N48" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="O48" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="P48" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="Q48" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="R48" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="S48" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="49" spans="1:19" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="49" spans="1:19">
       <c r="A49">
         <v>1</v>
       </c>
@@ -20635,7 +20638,7 @@
         <v>9171.7491640000007</v>
       </c>
     </row>
-    <row r="50" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:19">
       <c r="A50">
         <v>3</v>
       </c>
@@ -20685,7 +20688,7 @@
         <v>9173.2689329999994</v>
       </c>
     </row>
-    <row r="51" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:19">
       <c r="A51">
         <v>4</v>
       </c>
@@ -20735,7 +20738,7 @@
         <v>9152.5051110000004</v>
       </c>
     </row>
-    <row r="52" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:19">
       <c r="A52">
         <v>2</v>
       </c>
@@ -20785,7 +20788,7 @@
         <v>9158.1690249999992</v>
       </c>
     </row>
-    <row r="53" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:19">
       <c r="A53">
         <v>6</v>
       </c>
@@ -20835,7 +20838,7 @@
         <v>9135.2746869999992</v>
       </c>
     </row>
-    <row r="54" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:19">
       <c r="A54">
         <v>7</v>
       </c>
@@ -20885,7 +20888,7 @@
         <v>9151.8058099999998</v>
       </c>
     </row>
-    <row r="55" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:19">
       <c r="A55">
         <v>5</v>
       </c>
@@ -20935,7 +20938,7 @@
         <v>9157.8495669999993</v>
       </c>
     </row>
-    <row r="56" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:19">
       <c r="A56">
         <v>8</v>
       </c>
@@ -20985,7 +20988,7 @@
         <v>9131.1114030000008</v>
       </c>
     </row>
-    <row r="57" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:19">
       <c r="A57">
         <v>10</v>
       </c>
@@ -21035,7 +21038,7 @@
         <v>9134.1644359999991</v>
       </c>
     </row>
-    <row r="58" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:19">
       <c r="A58">
         <v>9</v>
       </c>
@@ -21085,9 +21088,9 @@
         <v>9127.0207119999995</v>
       </c>
     </row>
-    <row r="59" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:19">
       <c r="A59" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="B59">
         <f t="shared" ref="B59:H59" si="6">AVERAGE(B49:B58)</f>
@@ -21118,7 +21121,7 @@
         <v>17120.652057200001</v>
       </c>
       <c r="L59" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="M59">
         <f t="shared" ref="M59:S59" si="7">AVERAGE(M49:M58)</f>
@@ -21149,65 +21152,65 @@
         <v>9149.2918847999972</v>
       </c>
     </row>
-    <row r="62" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:19">
       <c r="A62" t="s">
+        <v>35</v>
+      </c>
+      <c r="L62" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="63" spans="1:19">
+      <c r="A63" t="s">
+        <v>17</v>
+      </c>
+      <c r="B63" t="s">
+        <v>18</v>
+      </c>
+      <c r="C63" t="s">
+        <v>19</v>
+      </c>
+      <c r="D63" t="s">
+        <v>20</v>
+      </c>
+      <c r="E63" t="s">
         <v>21</v>
       </c>
-      <c r="L62" t="s">
+      <c r="F63" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="63" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
-        <v>2</v>
-      </c>
-      <c r="B63" t="s">
-        <v>3</v>
-      </c>
-      <c r="C63" t="s">
-        <v>4</v>
-      </c>
-      <c r="D63" t="s">
-        <v>5</v>
-      </c>
-      <c r="E63" t="s">
-        <v>6</v>
-      </c>
-      <c r="F63" t="s">
-        <v>7</v>
-      </c>
       <c r="G63" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="H63" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="L63" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="M63" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="N63" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="O63" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="P63" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="Q63" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="R63" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="S63" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="64" spans="1:19" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="64" spans="1:19">
       <c r="A64">
         <v>1</v>
       </c>
@@ -21257,7 +21260,7 @@
         <v>8344.9795450000001</v>
       </c>
     </row>
-    <row r="65" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:19">
       <c r="A65">
         <v>3</v>
       </c>
@@ -21307,7 +21310,7 @@
         <v>8343.257173</v>
       </c>
     </row>
-    <row r="66" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:19">
       <c r="A66">
         <v>4</v>
       </c>
@@ -21357,7 +21360,7 @@
         <v>8310.7586979999996</v>
       </c>
     </row>
-    <row r="67" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:19">
       <c r="A67">
         <v>2</v>
       </c>
@@ -21407,7 +21410,7 @@
         <v>8322.7514780000001</v>
       </c>
     </row>
-    <row r="68" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:19">
       <c r="A68">
         <v>5</v>
       </c>
@@ -21457,7 +21460,7 @@
         <v>8315.7446419999997</v>
       </c>
     </row>
-    <row r="69" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:19">
       <c r="A69">
         <v>7</v>
       </c>
@@ -21507,7 +21510,7 @@
         <v>8313.8607919999995</v>
       </c>
     </row>
-    <row r="70" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:19">
       <c r="A70">
         <v>6</v>
       </c>
@@ -21557,7 +21560,7 @@
         <v>8303.0888589999995</v>
       </c>
     </row>
-    <row r="71" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:19">
       <c r="A71">
         <v>8</v>
       </c>
@@ -21607,7 +21610,7 @@
         <v>8305.1091159999996</v>
       </c>
     </row>
-    <row r="72" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:19">
       <c r="A72">
         <v>9</v>
       </c>
@@ -21657,7 +21660,7 @@
         <v>8302.2197579999993</v>
       </c>
     </row>
-    <row r="73" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:19">
       <c r="A73">
         <v>10</v>
       </c>
@@ -21707,9 +21710,9 @@
         <v>8310.8319300000003</v>
       </c>
     </row>
-    <row r="74" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:19">
       <c r="A74" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="B74">
         <f t="shared" ref="B74:H74" si="8">AVERAGE(B64:B73)</f>
@@ -21740,7 +21743,7 @@
         <v>17203.1997605</v>
       </c>
       <c r="L74" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="M74">
         <f t="shared" ref="M74:S74" si="9">AVERAGE(M64:M73)</f>
@@ -21771,65 +21774,65 @@
         <v>8317.2601990999992</v>
       </c>
     </row>
-    <row r="77" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:19">
       <c r="A77" t="s">
+        <v>37</v>
+      </c>
+      <c r="L77" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="78" spans="1:19">
+      <c r="A78" t="s">
+        <v>17</v>
+      </c>
+      <c r="B78" t="s">
+        <v>18</v>
+      </c>
+      <c r="C78" t="s">
+        <v>19</v>
+      </c>
+      <c r="D78" t="s">
+        <v>20</v>
+      </c>
+      <c r="E78" t="s">
+        <v>21</v>
+      </c>
+      <c r="F78" t="s">
+        <v>22</v>
+      </c>
+      <c r="G78" t="s">
         <v>23</v>
       </c>
-      <c r="L77" t="s">
+      <c r="H78" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="78" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
-        <v>2</v>
-      </c>
-      <c r="B78" t="s">
-        <v>3</v>
-      </c>
-      <c r="C78" t="s">
-        <v>4</v>
-      </c>
-      <c r="D78" t="s">
-        <v>5</v>
-      </c>
-      <c r="E78" t="s">
-        <v>6</v>
-      </c>
-      <c r="F78" t="s">
-        <v>7</v>
-      </c>
-      <c r="G78" t="s">
-        <v>8</v>
-      </c>
-      <c r="H78" t="s">
-        <v>9</v>
-      </c>
       <c r="L78" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="M78" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="N78" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="O78" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="P78" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="Q78" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="R78" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="S78" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="79" spans="1:19" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="79" spans="1:19">
       <c r="A79">
         <v>1</v>
       </c>
@@ -21879,7 +21882,7 @@
         <v>7663.0102479999996</v>
       </c>
     </row>
-    <row r="80" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:19">
       <c r="A80">
         <v>2</v>
       </c>
@@ -21929,7 +21932,7 @@
         <v>7659.1138490000003</v>
       </c>
     </row>
-    <row r="81" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:19">
       <c r="A81">
         <v>5</v>
       </c>
@@ -21979,7 +21982,7 @@
         <v>7623.4012519999997</v>
       </c>
     </row>
-    <row r="82" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:19">
       <c r="A82">
         <v>3</v>
       </c>
@@ -22029,7 +22032,7 @@
         <v>7638.5053660000003</v>
       </c>
     </row>
-    <row r="83" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:19">
       <c r="A83">
         <v>4</v>
       </c>
@@ -22079,7 +22082,7 @@
         <v>7622.947314</v>
       </c>
     </row>
-    <row r="84" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:19">
       <c r="A84">
         <v>7</v>
       </c>
@@ -22129,7 +22132,7 @@
         <v>7628.1462789999996</v>
       </c>
     </row>
-    <row r="85" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:19">
       <c r="A85">
         <v>6</v>
       </c>
@@ -22179,7 +22182,7 @@
         <v>7621.9801749999997</v>
       </c>
     </row>
-    <row r="86" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:19">
       <c r="A86">
         <v>9</v>
       </c>
@@ -22229,7 +22232,7 @@
         <v>7615.1883120000002</v>
       </c>
     </row>
-    <row r="87" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:19">
       <c r="A87">
         <v>10</v>
       </c>
@@ -22279,7 +22282,7 @@
         <v>7646.0684700000002</v>
       </c>
     </row>
-    <row r="88" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:19">
       <c r="A88">
         <v>8</v>
       </c>
@@ -22329,9 +22332,9 @@
         <v>7646.5795070000004</v>
       </c>
     </row>
-    <row r="89" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:19">
       <c r="A89" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="B89">
         <f t="shared" ref="B89:H89" si="10">AVERAGE(B79:B88)</f>
@@ -22362,7 +22365,7 @@
         <v>15228.365190699997</v>
       </c>
       <c r="L89" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="M89">
         <f t="shared" ref="M89:S89" si="11">AVERAGE(M79:M88)</f>
@@ -22401,82 +22404,82 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A2:Z89"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:26">
       <c r="A2" t="s">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="L2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:26">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D3" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L3" t="s">
+        <v>17</v>
+      </c>
+      <c r="M3" t="s">
+        <v>18</v>
+      </c>
+      <c r="N3" t="s">
+        <v>19</v>
+      </c>
+      <c r="O3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>22</v>
+      </c>
+      <c r="R3" t="s">
+        <v>23</v>
+      </c>
+      <c r="S3" t="s">
+        <v>24</v>
+      </c>
+      <c r="V3" t="s">
         <v>6</v>
       </c>
-      <c r="F3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H3" t="s">
-        <v>9</v>
-      </c>
-      <c r="L3" t="s">
-        <v>2</v>
-      </c>
-      <c r="M3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P3" t="s">
-        <v>6</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>7</v>
-      </c>
-      <c r="R3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S3" t="s">
-        <v>9</v>
-      </c>
-      <c r="V3" t="s">
-        <v>10</v>
-      </c>
       <c r="W3" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="X3" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="Y3" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="Z3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:26">
       <c r="A4">
         <v>6</v>
       </c>
@@ -22545,7 +22548,7 @@
         <v>5.2000000000000005E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:26">
       <c r="A5">
         <v>4</v>
       </c>
@@ -22614,7 +22617,7 @@
         <v>6.4000000000000015E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:26">
       <c r="A6">
         <v>5</v>
       </c>
@@ -22683,7 +22686,7 @@
         <v>5.6000000000000008E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:26">
       <c r="A7">
         <v>2</v>
       </c>
@@ -22752,7 +22755,7 @@
         <v>5.3000000000000005E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:26">
       <c r="A8">
         <v>9</v>
       </c>
@@ -22821,7 +22824,7 @@
         <v>0.11899999999999999</v>
       </c>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:26">
       <c r="A9">
         <v>7</v>
       </c>
@@ -22890,7 +22893,7 @@
         <v>6.0000000000000012E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:26">
       <c r="A10">
         <v>3</v>
       </c>
@@ -22959,7 +22962,7 @@
         <v>4.9999999999999996E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:26">
       <c r="A11">
         <v>10</v>
       </c>
@@ -23028,7 +23031,7 @@
         <v>9.2999999999999985E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:26">
       <c r="A12">
         <v>1</v>
       </c>
@@ -23097,7 +23100,7 @@
         <v>5.2000000000000005E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:26">
       <c r="A13">
         <v>8</v>
       </c>
@@ -23166,9 +23169,9 @@
         <v>3.7999999999999992E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:26">
       <c r="A14" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="B14">
         <f t="shared" ref="B14:H14" si="0">AVERAGE(B4:B13)</f>
@@ -23199,7 +23202,7 @@
         <v>17040.629265700001</v>
       </c>
       <c r="L14" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="M14">
         <f t="shared" ref="M14:S14" si="1">AVERAGE(M4:M13)</f>
@@ -23249,7 +23252,7 @@
         <v>0.14499999999999996</v>
       </c>
     </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:26">
       <c r="V15">
         <v>1536</v>
       </c>
@@ -23270,65 +23273,65 @@
         <v>3.2999999999999995E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:19">
       <c r="A17" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="L17" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19">
       <c r="A18" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="C18" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D18" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E18" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="F18" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="G18" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="H18" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="L18" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="M18" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="N18" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="O18" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="P18" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="Q18" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="R18" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="S18" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19">
       <c r="A19">
         <v>1</v>
       </c>
@@ -23378,7 +23381,7 @@
         <v>11404.073166</v>
       </c>
     </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:19">
       <c r="A20">
         <v>5</v>
       </c>
@@ -23428,7 +23431,7 @@
         <v>11402.257922000001</v>
       </c>
     </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:19">
       <c r="A21">
         <v>9</v>
       </c>
@@ -23478,7 +23481,7 @@
         <v>11375.874845</v>
       </c>
     </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:19">
       <c r="A22">
         <v>2</v>
       </c>
@@ -23528,7 +23531,7 @@
         <v>11375.628346</v>
       </c>
     </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:19">
       <c r="A23">
         <v>8</v>
       </c>
@@ -23578,7 +23581,7 @@
         <v>11377.034785</v>
       </c>
     </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:19">
       <c r="A24">
         <v>10</v>
       </c>
@@ -23628,7 +23631,7 @@
         <v>11375.397720999999</v>
       </c>
     </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:19">
       <c r="A25">
         <v>3</v>
       </c>
@@ -23678,7 +23681,7 @@
         <v>11376.237907000001</v>
       </c>
     </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:19">
       <c r="A26">
         <v>6</v>
       </c>
@@ -23728,7 +23731,7 @@
         <v>11377.790234</v>
       </c>
     </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:19">
       <c r="A27">
         <v>7</v>
       </c>
@@ -23778,7 +23781,7 @@
         <v>11376.826423</v>
       </c>
     </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:19">
       <c r="A28">
         <v>4</v>
       </c>
@@ -23828,9 +23831,9 @@
         <v>11376.265839</v>
       </c>
     </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:19">
       <c r="A29" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="B29">
         <f t="shared" ref="B29:H29" si="2">AVERAGE(B19:B28)</f>
@@ -23861,7 +23864,7 @@
         <v>17051.102983600002</v>
       </c>
       <c r="L29" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="M29">
         <f t="shared" ref="M29:S29" si="3">AVERAGE(M19:M28)</f>
@@ -23892,65 +23895,65 @@
         <v>11381.738718800001</v>
       </c>
     </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:19">
       <c r="A32" t="s">
+        <v>31</v>
+      </c>
+      <c r="L32" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19">
+      <c r="A33" t="s">
         <v>17</v>
       </c>
-      <c r="L32" t="s">
+      <c r="B33" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>2</v>
-      </c>
-      <c r="B33" t="s">
-        <v>3</v>
-      </c>
       <c r="C33" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D33" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E33" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="F33" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="G33" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="H33" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="L33" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="M33" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="N33" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="O33" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="P33" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="Q33" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="R33" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="S33" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19">
       <c r="A34">
         <v>6</v>
       </c>
@@ -24000,7 +24003,7 @@
         <v>10234.801020999999</v>
       </c>
     </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:19">
       <c r="A35">
         <v>8</v>
       </c>
@@ -24050,7 +24053,7 @@
         <v>10234.704771999999</v>
       </c>
     </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:19">
       <c r="A36">
         <v>10</v>
       </c>
@@ -24100,7 +24103,7 @@
         <v>10193.959159</v>
       </c>
     </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:19">
       <c r="A37">
         <v>1</v>
       </c>
@@ -24150,7 +24153,7 @@
         <v>10193.536174999999</v>
       </c>
     </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:19">
       <c r="A38">
         <v>4</v>
       </c>
@@ -24200,7 +24203,7 @@
         <v>10192.396427</v>
       </c>
     </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:19">
       <c r="A39">
         <v>5</v>
       </c>
@@ -24250,7 +24253,7 @@
         <v>10192.687362000001</v>
       </c>
     </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:19">
       <c r="A40">
         <v>3</v>
       </c>
@@ -24300,7 +24303,7 @@
         <v>10193.708753999999</v>
       </c>
     </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:19">
       <c r="A41">
         <v>2</v>
       </c>
@@ -24350,7 +24353,7 @@
         <v>10193.94291</v>
       </c>
     </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:19">
       <c r="A42">
         <v>7</v>
       </c>
@@ -24400,7 +24403,7 @@
         <v>10192.656236999999</v>
       </c>
     </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:19">
       <c r="A43">
         <v>9</v>
       </c>
@@ -24450,9 +24453,9 @@
         <v>10194.09139</v>
       </c>
     </row>
-    <row r="44" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:19">
       <c r="A44" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="B44">
         <f t="shared" ref="B44:H44" si="4">AVERAGE(B34:B43)</f>
@@ -24483,7 +24486,7 @@
         <v>17023.263080700002</v>
       </c>
       <c r="L44" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="M44">
         <f t="shared" ref="M44:S44" si="5">AVERAGE(M34:M43)</f>
@@ -24514,65 +24517,65 @@
         <v>10201.648420699999</v>
       </c>
     </row>
-    <row r="47" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:19">
       <c r="A47" t="s">
+        <v>33</v>
+      </c>
+      <c r="L47" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="48" spans="1:19">
+      <c r="A48" t="s">
+        <v>17</v>
+      </c>
+      <c r="B48" t="s">
+        <v>18</v>
+      </c>
+      <c r="C48" t="s">
         <v>19</v>
       </c>
-      <c r="L47" t="s">
+      <c r="D48" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="48" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>2</v>
-      </c>
-      <c r="B48" t="s">
-        <v>3</v>
-      </c>
-      <c r="C48" t="s">
-        <v>4</v>
-      </c>
-      <c r="D48" t="s">
-        <v>5</v>
-      </c>
       <c r="E48" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="F48" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="G48" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="H48" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="L48" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="M48" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="N48" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="O48" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="P48" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="Q48" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="R48" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="S48" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="49" spans="1:19" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="49" spans="1:19">
       <c r="A49">
         <v>1</v>
       </c>
@@ -24622,7 +24625,7 @@
         <v>9271.1302599999999</v>
       </c>
     </row>
-    <row r="50" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:19">
       <c r="A50">
         <v>5</v>
       </c>
@@ -24672,7 +24675,7 @@
         <v>9270.6380069999996</v>
       </c>
     </row>
-    <row r="51" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:19">
       <c r="A51">
         <v>7</v>
       </c>
@@ -24722,7 +24725,7 @@
         <v>9228.2844850000001</v>
       </c>
     </row>
-    <row r="52" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:19">
       <c r="A52">
         <v>4</v>
       </c>
@@ -24772,7 +24775,7 @@
         <v>9226.4057460000004</v>
       </c>
     </row>
-    <row r="53" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:19">
       <c r="A53">
         <v>9</v>
       </c>
@@ -24822,7 +24825,7 @@
         <v>9226.8157439999995</v>
       </c>
     </row>
-    <row r="54" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:19">
       <c r="A54">
         <v>2</v>
       </c>
@@ -24872,7 +24875,7 @@
         <v>9226.5431279999993</v>
       </c>
     </row>
-    <row r="55" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:19">
       <c r="A55">
         <v>6</v>
       </c>
@@ -24922,7 +24925,7 @@
         <v>9224.9738510000006</v>
       </c>
     </row>
-    <row r="56" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:19">
       <c r="A56">
         <v>10</v>
       </c>
@@ -24972,7 +24975,7 @@
         <v>9226.4346150000001</v>
       </c>
     </row>
-    <row r="57" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:19">
       <c r="A57">
         <v>8</v>
       </c>
@@ -25022,7 +25025,7 @@
         <v>9225.8011760000009</v>
       </c>
     </row>
-    <row r="58" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:19">
       <c r="A58">
         <v>3</v>
       </c>
@@ -25072,9 +25075,9 @@
         <v>9226.1957710000006</v>
       </c>
     </row>
-    <row r="59" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:19">
       <c r="A59" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="B59">
         <f t="shared" ref="B59:H59" si="6">AVERAGE(B49:B58)</f>
@@ -25105,7 +25108,7 @@
         <v>17032.817082100002</v>
       </c>
       <c r="L59" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="M59">
         <f t="shared" ref="M59:S59" si="7">AVERAGE(M49:M58)</f>
@@ -25136,65 +25139,65 @@
         <v>9235.3222783000001</v>
       </c>
     </row>
-    <row r="62" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:19">
       <c r="A62" t="s">
+        <v>35</v>
+      </c>
+      <c r="L62" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="63" spans="1:19">
+      <c r="A63" t="s">
+        <v>17</v>
+      </c>
+      <c r="B63" t="s">
+        <v>18</v>
+      </c>
+      <c r="C63" t="s">
+        <v>19</v>
+      </c>
+      <c r="D63" t="s">
+        <v>20</v>
+      </c>
+      <c r="E63" t="s">
         <v>21</v>
       </c>
-      <c r="L62" t="s">
+      <c r="F63" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="63" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
-        <v>2</v>
-      </c>
-      <c r="B63" t="s">
-        <v>3</v>
-      </c>
-      <c r="C63" t="s">
-        <v>4</v>
-      </c>
-      <c r="D63" t="s">
-        <v>5</v>
-      </c>
-      <c r="E63" t="s">
-        <v>6</v>
-      </c>
-      <c r="F63" t="s">
-        <v>7</v>
-      </c>
       <c r="G63" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="H63" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="L63" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="M63" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="N63" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="O63" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="P63" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="Q63" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="R63" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="S63" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="64" spans="1:19" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="64" spans="1:19">
       <c r="A64">
         <v>5</v>
       </c>
@@ -25244,7 +25247,7 @@
         <v>8493.8242399999999</v>
       </c>
     </row>
-    <row r="65" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:19">
       <c r="A65">
         <v>2</v>
       </c>
@@ -25294,7 +25297,7 @@
         <v>8493.2597819999992</v>
       </c>
     </row>
-    <row r="66" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:19">
       <c r="A66">
         <v>8</v>
       </c>
@@ -25344,7 +25347,7 @@
         <v>8432.7432750000007</v>
       </c>
     </row>
-    <row r="67" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:19">
       <c r="A67">
         <v>3</v>
       </c>
@@ -25394,7 +25397,7 @@
         <v>8432.030444</v>
       </c>
     </row>
-    <row r="68" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:19">
       <c r="A68">
         <v>6</v>
       </c>
@@ -25444,7 +25447,7 @@
         <v>8430.3814719999991</v>
       </c>
     </row>
-    <row r="69" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:19">
       <c r="A69">
         <v>4</v>
       </c>
@@ -25494,7 +25497,7 @@
         <v>8430.0125960000005</v>
       </c>
     </row>
-    <row r="70" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:19">
       <c r="A70">
         <v>9</v>
       </c>
@@ -25544,7 +25547,7 @@
         <v>8429.8776909999997</v>
       </c>
     </row>
-    <row r="71" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:19">
       <c r="A71">
         <v>7</v>
       </c>
@@ -25594,7 +25597,7 @@
         <v>8430.4952630000007</v>
       </c>
     </row>
-    <row r="72" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:19">
       <c r="A72">
         <v>10</v>
       </c>
@@ -25644,7 +25647,7 @@
         <v>8429.9498320000002</v>
       </c>
     </row>
-    <row r="73" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:19">
       <c r="A73">
         <v>1</v>
       </c>
@@ -25694,9 +25697,9 @@
         <v>8430.5734909999992</v>
       </c>
     </row>
-    <row r="74" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:19">
       <c r="A74" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="B74">
         <f t="shared" ref="B74:H74" si="8">AVERAGE(B64:B73)</f>
@@ -25727,7 +25730,7 @@
         <v>17051.784170200001</v>
       </c>
       <c r="L74" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="M74">
         <f t="shared" ref="M74:S74" si="9">AVERAGE(M64:M73)</f>
@@ -25758,65 +25761,65 @@
         <v>8443.3148086000001</v>
       </c>
     </row>
-    <row r="77" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:19">
       <c r="A77" t="s">
+        <v>37</v>
+      </c>
+      <c r="L77" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="78" spans="1:19">
+      <c r="A78" t="s">
+        <v>17</v>
+      </c>
+      <c r="B78" t="s">
+        <v>18</v>
+      </c>
+      <c r="C78" t="s">
+        <v>19</v>
+      </c>
+      <c r="D78" t="s">
+        <v>20</v>
+      </c>
+      <c r="E78" t="s">
+        <v>21</v>
+      </c>
+      <c r="F78" t="s">
+        <v>22</v>
+      </c>
+      <c r="G78" t="s">
         <v>23</v>
       </c>
-      <c r="L77" t="s">
+      <c r="H78" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="78" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
-        <v>2</v>
-      </c>
-      <c r="B78" t="s">
-        <v>3</v>
-      </c>
-      <c r="C78" t="s">
-        <v>4</v>
-      </c>
-      <c r="D78" t="s">
-        <v>5</v>
-      </c>
-      <c r="E78" t="s">
-        <v>6</v>
-      </c>
-      <c r="F78" t="s">
-        <v>7</v>
-      </c>
-      <c r="G78" t="s">
-        <v>8</v>
-      </c>
-      <c r="H78" t="s">
-        <v>9</v>
-      </c>
       <c r="L78" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="M78" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="N78" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="O78" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="P78" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="Q78" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="R78" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="S78" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="79" spans="1:19" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="79" spans="1:19">
       <c r="A79">
         <v>1</v>
       </c>
@@ -25866,7 +25869,7 @@
         <v>7535.4684779999998</v>
       </c>
     </row>
-    <row r="80" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:19">
       <c r="A80">
         <v>6</v>
       </c>
@@ -25916,7 +25919,7 @@
         <v>7535.506085</v>
       </c>
     </row>
-    <row r="81" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:19">
       <c r="A81">
         <v>7</v>
       </c>
@@ -25966,7 +25969,7 @@
         <v>7461.1208790000001</v>
       </c>
     </row>
-    <row r="82" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:19">
       <c r="A82">
         <v>5</v>
       </c>
@@ -26016,7 +26019,7 @@
         <v>7457.874828</v>
       </c>
     </row>
-    <row r="83" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:19">
       <c r="A83">
         <v>10</v>
       </c>
@@ -26066,7 +26069,7 @@
         <v>7458.4546</v>
       </c>
     </row>
-    <row r="84" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:19">
       <c r="A84">
         <v>9</v>
       </c>
@@ -26116,7 +26119,7 @@
         <v>7458.2198749999998</v>
       </c>
     </row>
-    <row r="85" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:19">
       <c r="A85">
         <v>3</v>
       </c>
@@ -26166,7 +26169,7 @@
         <v>7458.2383639999998</v>
       </c>
     </row>
-    <row r="86" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:19">
       <c r="A86">
         <v>2</v>
       </c>
@@ -26216,7 +26219,7 @@
         <v>7458.7753620000003</v>
       </c>
     </row>
-    <row r="87" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:19">
       <c r="A87">
         <v>4</v>
       </c>
@@ -26266,7 +26269,7 @@
         <v>7458.7785009999998</v>
       </c>
     </row>
-    <row r="88" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:19">
       <c r="A88">
         <v>8</v>
       </c>
@@ -26316,9 +26319,9 @@
         <v>7459.4933959999998</v>
       </c>
     </row>
-    <row r="89" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:19">
       <c r="A89" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="B89">
         <f t="shared" ref="B89:H89" si="10">AVERAGE(B79:B88)</f>
@@ -26349,7 +26352,7 @@
         <v>14825.445759499999</v>
       </c>
       <c r="L89" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="M89">
         <f t="shared" ref="M89:S89" si="11">AVERAGE(M79:M88)</f>
